--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/ene-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/ene-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC ene-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC ene-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8235,7 +8235,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9089,7 +9089,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -9150,7 +9150,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9577,7 +9577,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10187,7 +10187,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10309,7 +10309,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10370,7 +10370,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10431,7 +10431,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10492,7 +10492,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10553,7 +10553,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10919,7 +10919,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10980,7 +10980,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -11102,7 +11102,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -11163,7 +11163,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -11224,7 +11224,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11407,7 +11407,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11529,7 +11529,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -11590,7 +11590,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11712,7 +11712,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -11773,7 +11773,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -11834,7 +11834,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -11956,7 +11956,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -12261,7 +12261,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12322,7 +12322,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -12383,7 +12383,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -12444,7 +12444,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12505,7 +12505,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -12627,7 +12627,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -12688,7 +12688,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -12810,7 +12810,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -12871,7 +12871,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -12932,7 +12932,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -12993,7 +12993,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13054,7 +13054,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -13115,7 +13115,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -13176,7 +13176,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -13298,7 +13298,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -13359,7 +13359,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -13420,7 +13420,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -13481,7 +13481,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -13542,7 +13542,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -13603,7 +13603,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -13786,7 +13786,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -13847,7 +13847,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -13908,7 +13908,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -13969,7 +13969,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -14030,7 +14030,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -14091,7 +14091,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -14152,7 +14152,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -14213,7 +14213,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -14274,7 +14274,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -14396,7 +14396,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -14518,7 +14518,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -14579,7 +14579,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -14640,7 +14640,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -14884,7 +14884,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -14945,7 +14945,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -15006,7 +15006,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -15067,7 +15067,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -15128,7 +15128,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -15189,7 +15189,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -15250,7 +15250,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -15311,7 +15311,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -15372,7 +15372,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -15433,7 +15433,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -15494,7 +15494,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -15555,7 +15555,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -15616,7 +15616,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -15677,7 +15677,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -15738,7 +15738,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -15799,7 +15799,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -15860,7 +15860,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -15921,7 +15921,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -15982,7 +15982,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -16043,7 +16043,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -16104,7 +16104,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -16165,7 +16165,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -16226,7 +16226,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -16287,7 +16287,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -16409,7 +16409,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -16470,7 +16470,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -16531,7 +16531,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -16714,7 +16714,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -16836,7 +16836,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -16897,7 +16897,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -16958,7 +16958,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -17019,7 +17019,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -17080,7 +17080,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -17141,7 +17141,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -17324,7 +17324,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -17385,7 +17385,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -17446,7 +17446,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -17507,7 +17507,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -17568,7 +17568,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -17629,7 +17629,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -17690,7 +17690,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -17751,7 +17751,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -17812,7 +17812,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -17873,7 +17873,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -17995,7 +17995,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -18056,7 +18056,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -18117,7 +18117,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -18178,7 +18178,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -18300,7 +18300,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -18361,7 +18361,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -18544,7 +18544,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -18605,7 +18605,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -18666,7 +18666,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -18727,7 +18727,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -18788,7 +18788,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -18849,7 +18849,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -18910,7 +18910,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -19032,7 +19032,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -19093,7 +19093,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -19154,7 +19154,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -19215,7 +19215,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -19337,7 +19337,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -19398,7 +19398,7 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -19459,7 +19459,7 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -19520,7 +19520,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -19581,7 +19581,7 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -19642,7 +19642,7 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -19703,7 +19703,7 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -19764,7 +19764,7 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -19825,7 +19825,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -19886,7 +19886,7 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -19947,7 +19947,7 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -20008,7 +20008,7 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -20069,7 +20069,7 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -20130,7 +20130,7 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -20191,7 +20191,7 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -20252,7 +20252,7 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -20313,7 +20313,7 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -20374,7 +20374,7 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -20435,7 +20435,7 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -20496,7 +20496,7 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -20557,7 +20557,7 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -20618,7 +20618,7 @@
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
@@ -20740,7 +20740,7 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -20801,7 +20801,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -20862,7 +20862,7 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -20923,7 +20923,7 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -20984,7 +20984,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -21045,7 +21045,7 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -21106,7 +21106,7 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -21167,7 +21167,7 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -21228,7 +21228,7 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -21289,7 +21289,7 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -21350,7 +21350,7 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -21411,7 +21411,7 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -21472,7 +21472,7 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -21533,7 +21533,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -21594,7 +21594,7 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -21655,7 +21655,7 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
@@ -21716,7 +21716,7 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -21777,7 +21777,7 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -21838,7 +21838,7 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -21899,7 +21899,7 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
@@ -22021,7 +22021,7 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
@@ -22082,7 +22082,7 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -22143,7 +22143,7 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -22265,7 +22265,7 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -22326,7 +22326,7 @@
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
@@ -22387,7 +22387,7 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
@@ -22448,7 +22448,7 @@
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
@@ -22570,7 +22570,7 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
@@ -22631,7 +22631,7 @@
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
@@ -22692,7 +22692,7 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
@@ -22753,7 +22753,7 @@
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
@@ -22814,7 +22814,7 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
@@ -22875,7 +22875,7 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
@@ -22936,7 +22936,7 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -22997,7 +22997,7 @@
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
@@ -23058,7 +23058,7 @@
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
@@ -23180,7 +23180,7 @@
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
@@ -23241,7 +23241,7 @@
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
@@ -23302,7 +23302,7 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -23363,7 +23363,7 @@
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
@@ -23424,7 +23424,7 @@
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
@@ -23485,7 +23485,7 @@
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
@@ -23546,7 +23546,7 @@
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
@@ -23607,7 +23607,7 @@
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
@@ -23668,7 +23668,7 @@
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
@@ -23729,7 +23729,7 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
@@ -23790,7 +23790,7 @@
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
@@ -23851,7 +23851,7 @@
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -23912,7 +23912,7 @@
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
@@ -23973,7 +23973,7 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -24034,7 +24034,7 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
@@ -24095,7 +24095,7 @@
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
@@ -24156,7 +24156,7 @@
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
@@ -24217,7 +24217,7 @@
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
@@ -24278,7 +24278,7 @@
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
@@ -24339,7 +24339,7 @@
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
@@ -24400,7 +24400,7 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
@@ -24461,7 +24461,7 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
@@ -24583,7 +24583,7 @@
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
@@ -24644,7 +24644,7 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
@@ -24705,7 +24705,7 @@
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
@@ -24766,7 +24766,7 @@
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
@@ -24827,7 +24827,7 @@
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
@@ -24888,7 +24888,7 @@
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I401" t="inlineStr">
@@ -24949,7 +24949,7 @@
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
@@ -25010,7 +25010,7 @@
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I403" t="inlineStr">
@@ -25132,7 +25132,7 @@
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
@@ -25254,7 +25254,7 @@
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I407" t="inlineStr">
@@ -25315,7 +25315,7 @@
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
@@ -25376,7 +25376,7 @@
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I409" t="inlineStr">
@@ -25437,7 +25437,7 @@
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I410" t="inlineStr">
@@ -25498,7 +25498,7 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
@@ -25559,7 +25559,7 @@
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
@@ -25620,7 +25620,7 @@
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I413" t="inlineStr">
@@ -25681,7 +25681,7 @@
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I414" t="inlineStr">
@@ -25742,7 +25742,7 @@
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I415" t="inlineStr">
@@ -25803,7 +25803,7 @@
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I416" t="inlineStr">
@@ -25864,7 +25864,7 @@
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I417" t="inlineStr">
@@ -25925,7 +25925,7 @@
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
@@ -25986,7 +25986,7 @@
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I419" t="inlineStr">
@@ -26047,7 +26047,7 @@
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I420" t="inlineStr">
@@ -26108,7 +26108,7 @@
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I421" t="inlineStr">
@@ -26169,7 +26169,7 @@
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
@@ -26230,7 +26230,7 @@
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I423" t="inlineStr">
@@ -26291,7 +26291,7 @@
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
@@ -26352,7 +26352,7 @@
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
@@ -26413,7 +26413,7 @@
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
@@ -26474,7 +26474,7 @@
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
@@ -26535,7 +26535,7 @@
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I428" t="inlineStr">
@@ -26596,7 +26596,7 @@
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
@@ -26657,7 +26657,7 @@
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
@@ -26718,7 +26718,7 @@
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
@@ -26779,7 +26779,7 @@
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
@@ -26840,7 +26840,7 @@
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
@@ -26901,7 +26901,7 @@
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
@@ -26962,7 +26962,7 @@
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
@@ -27023,7 +27023,7 @@
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
@@ -27084,7 +27084,7 @@
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
@@ -27145,7 +27145,7 @@
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
@@ -27206,7 +27206,7 @@
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I439" t="inlineStr">
@@ -27267,7 +27267,7 @@
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I440" t="inlineStr">
@@ -27328,7 +27328,7 @@
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
@@ -27389,7 +27389,7 @@
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I442" t="inlineStr">
@@ -27450,7 +27450,7 @@
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I443" t="inlineStr">
@@ -27511,7 +27511,7 @@
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I444" t="inlineStr">
@@ -27633,7 +27633,7 @@
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
@@ -27694,7 +27694,7 @@
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I447" t="inlineStr">
@@ -27755,7 +27755,7 @@
       </c>
       <c r="H448" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I448" t="inlineStr">
@@ -27816,7 +27816,7 @@
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
@@ -27877,7 +27877,7 @@
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I450" t="inlineStr">
@@ -27938,7 +27938,7 @@
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I451" t="inlineStr">
@@ -28060,7 +28060,7 @@
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I453" t="inlineStr">
@@ -28121,7 +28121,7 @@
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I454" t="inlineStr">
@@ -28182,7 +28182,7 @@
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
@@ -28243,7 +28243,7 @@
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I456" t="inlineStr">
@@ -28304,7 +28304,7 @@
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I457" t="inlineStr">
@@ -28365,7 +28365,7 @@
       </c>
       <c r="H458" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I458" t="inlineStr">
@@ -28426,7 +28426,7 @@
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I459" t="inlineStr">
@@ -28487,7 +28487,7 @@
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I460" t="inlineStr">
@@ -28548,7 +28548,7 @@
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I461" t="inlineStr">
@@ -28609,7 +28609,7 @@
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I462" t="inlineStr">
@@ -28670,7 +28670,7 @@
       </c>
       <c r="H463" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I463" t="inlineStr">
@@ -28731,7 +28731,7 @@
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I464" t="inlineStr">
@@ -28792,7 +28792,7 @@
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
@@ -28853,7 +28853,7 @@
       </c>
       <c r="H466" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I466" t="inlineStr">
@@ -28914,7 +28914,7 @@
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
@@ -28975,7 +28975,7 @@
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I468" t="inlineStr">
@@ -29036,7 +29036,7 @@
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I469" t="inlineStr">
@@ -29097,7 +29097,7 @@
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I470" t="inlineStr">
@@ -29158,7 +29158,7 @@
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I471" t="inlineStr">
@@ -29219,7 +29219,7 @@
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I472" t="inlineStr">
@@ -29280,7 +29280,7 @@
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I473" t="inlineStr">
@@ -29341,7 +29341,7 @@
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I474" t="inlineStr">
@@ -29402,7 +29402,7 @@
       </c>
       <c r="H475" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I475" t="inlineStr">
@@ -29463,7 +29463,7 @@
       </c>
       <c r="H476" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I476" t="inlineStr">
@@ -29524,7 +29524,7 @@
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I477" t="inlineStr">
@@ -29585,7 +29585,7 @@
       </c>
       <c r="H478" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I478" t="inlineStr">
@@ -29646,7 +29646,7 @@
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I479" t="inlineStr">
@@ -29707,7 +29707,7 @@
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I480" t="inlineStr">
@@ -29768,7 +29768,7 @@
       </c>
       <c r="H481" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I481" t="inlineStr">
@@ -29829,7 +29829,7 @@
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I482" t="inlineStr">
@@ -29890,7 +29890,7 @@
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I483" t="inlineStr">
@@ -29951,7 +29951,7 @@
       </c>
       <c r="H484" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I484" t="inlineStr">
@@ -30012,7 +30012,7 @@
       </c>
       <c r="H485" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I485" t="inlineStr">
@@ -30134,7 +30134,7 @@
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I487" t="inlineStr">
@@ -30256,7 +30256,7 @@
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I489" t="inlineStr">
@@ -30317,7 +30317,7 @@
       </c>
       <c r="H490" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I490" t="inlineStr">
@@ -30378,7 +30378,7 @@
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I491" t="inlineStr">
@@ -30439,7 +30439,7 @@
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I492" t="inlineStr">
@@ -30500,7 +30500,7 @@
       </c>
       <c r="H493" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I493" t="inlineStr">
@@ -30561,7 +30561,7 @@
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I494" t="inlineStr">
@@ -30622,7 +30622,7 @@
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I495" t="inlineStr">
@@ -30683,7 +30683,7 @@
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I496" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I497" t="inlineStr">
@@ -30805,7 +30805,7 @@
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I498" t="inlineStr">
@@ -30866,7 +30866,7 @@
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I499" t="inlineStr">
@@ -30927,7 +30927,7 @@
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I500" t="inlineStr">
@@ -30988,7 +30988,7 @@
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I501" t="inlineStr">
@@ -31049,7 +31049,7 @@
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I502" t="inlineStr">
@@ -31110,7 +31110,7 @@
       </c>
       <c r="H503" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I503" t="inlineStr">
@@ -31171,7 +31171,7 @@
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I504" t="inlineStr">
@@ -31232,7 +31232,7 @@
       </c>
       <c r="H505" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I505" t="inlineStr">
@@ -31293,7 +31293,7 @@
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I506" t="inlineStr">
@@ -31354,7 +31354,7 @@
       </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I507" t="inlineStr">
@@ -31415,7 +31415,7 @@
       </c>
       <c r="H508" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I508" t="inlineStr">
@@ -31476,7 +31476,7 @@
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I509" t="inlineStr">
@@ -31537,7 +31537,7 @@
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I510" t="inlineStr">
@@ -31598,7 +31598,7 @@
       </c>
       <c r="H511" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I511" t="inlineStr">
@@ -31659,7 +31659,7 @@
       </c>
       <c r="H512" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I512" t="inlineStr">
@@ -31720,7 +31720,7 @@
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I513" t="inlineStr">
@@ -31781,7 +31781,7 @@
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I514" t="inlineStr">
@@ -31842,7 +31842,7 @@
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I515" t="inlineStr">
@@ -31903,7 +31903,7 @@
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I516" t="inlineStr">
@@ -31964,7 +31964,7 @@
       </c>
       <c r="H517" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I517" t="inlineStr">
@@ -32025,7 +32025,7 @@
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I518" t="inlineStr">
@@ -32086,7 +32086,7 @@
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I519" t="inlineStr">
@@ -32147,7 +32147,7 @@
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I520" t="inlineStr">
@@ -32330,7 +32330,7 @@
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I523" t="inlineStr">
@@ -32391,7 +32391,7 @@
       </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I524" t="inlineStr">
@@ -32452,7 +32452,7 @@
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I525" t="inlineStr">
@@ -32513,7 +32513,7 @@
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I526" t="inlineStr">
@@ -32635,7 +32635,7 @@
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I528" t="inlineStr">
@@ -32696,7 +32696,7 @@
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I529" t="inlineStr">
@@ -32757,7 +32757,7 @@
       </c>
       <c r="H530" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
@@ -32818,7 +32818,7 @@
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I531" t="inlineStr">
@@ -32879,7 +32879,7 @@
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
@@ -32940,7 +32940,7 @@
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
@@ -33001,7 +33001,7 @@
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I534" t="inlineStr">
@@ -33062,7 +33062,7 @@
       </c>
       <c r="H535" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I535" t="inlineStr">
@@ -33123,7 +33123,7 @@
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I536" t="inlineStr">
@@ -33184,7 +33184,7 @@
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I537" t="inlineStr">
@@ -33245,7 +33245,7 @@
       </c>
       <c r="H538" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I538" t="inlineStr">
@@ -33306,7 +33306,7 @@
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I539" t="inlineStr">
@@ -33367,7 +33367,7 @@
       </c>
       <c r="H540" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I540" t="inlineStr">
@@ -33428,7 +33428,7 @@
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I541" t="inlineStr">
@@ -33489,7 +33489,7 @@
       </c>
       <c r="H542" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I542" t="inlineStr">
@@ -33550,7 +33550,7 @@
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I543" t="inlineStr">
@@ -33611,7 +33611,7 @@
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I544" t="inlineStr">
@@ -33672,7 +33672,7 @@
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I545" t="inlineStr">
@@ -33733,7 +33733,7 @@
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I546" t="inlineStr">
@@ -33794,7 +33794,7 @@
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
@@ -33855,7 +33855,7 @@
       </c>
       <c r="H548" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I548" t="inlineStr">
@@ -33916,7 +33916,7 @@
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I549" t="inlineStr">
@@ -33977,7 +33977,7 @@
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I550" t="inlineStr">
@@ -34038,7 +34038,7 @@
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I551" t="inlineStr">
@@ -34099,7 +34099,7 @@
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I552" t="inlineStr">
@@ -34160,7 +34160,7 @@
       </c>
       <c r="H553" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I553" t="inlineStr">
@@ -34282,7 +34282,7 @@
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I555" t="inlineStr">
@@ -34343,7 +34343,7 @@
       </c>
       <c r="H556" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I556" t="inlineStr">
@@ -34404,7 +34404,7 @@
       </c>
       <c r="H557" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I557" t="inlineStr">
@@ -34465,7 +34465,7 @@
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I558" t="inlineStr">
@@ -34526,7 +34526,7 @@
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I559" t="inlineStr">
@@ -34587,7 +34587,7 @@
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I560" t="inlineStr">
@@ -34648,7 +34648,7 @@
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I561" t="inlineStr">
@@ -34709,7 +34709,7 @@
       </c>
       <c r="H562" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I562" t="inlineStr">
@@ -34770,7 +34770,7 @@
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I563" t="inlineStr">
@@ -34892,7 +34892,7 @@
       </c>
       <c r="H565" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I565" t="inlineStr">
@@ -34953,7 +34953,7 @@
       </c>
       <c r="H566" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I566" t="inlineStr">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I567" t="inlineStr">
@@ -35075,7 +35075,7 @@
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I568" t="inlineStr">
@@ -35136,7 +35136,7 @@
       </c>
       <c r="H569" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I569" t="inlineStr">
@@ -35197,7 +35197,7 @@
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I570" t="inlineStr">
@@ -35258,7 +35258,7 @@
       </c>
       <c r="H571" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I571" t="inlineStr">
@@ -35319,7 +35319,7 @@
       </c>
       <c r="H572" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I572" t="inlineStr">
@@ -35380,7 +35380,7 @@
       </c>
       <c r="H573" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I573" t="inlineStr">
@@ -35441,7 +35441,7 @@
       </c>
       <c r="H574" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I574" t="inlineStr">
@@ -35502,7 +35502,7 @@
       </c>
       <c r="H575" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I575" t="inlineStr">
@@ -35563,7 +35563,7 @@
       </c>
       <c r="H576" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I576" t="inlineStr">
@@ -35624,7 +35624,7 @@
       </c>
       <c r="H577" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I577" t="inlineStr">
@@ -35685,7 +35685,7 @@
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I578" t="inlineStr">
@@ -35746,7 +35746,7 @@
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I579" t="inlineStr">
@@ -35807,7 +35807,7 @@
       </c>
       <c r="H580" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I580" t="inlineStr">
@@ -35868,7 +35868,7 @@
       </c>
       <c r="H581" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I581" t="inlineStr">
@@ -35929,7 +35929,7 @@
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I582" t="inlineStr">
@@ -35990,7 +35990,7 @@
       </c>
       <c r="H583" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I583" t="inlineStr">
@@ -36051,7 +36051,7 @@
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I584" t="inlineStr">
@@ -36112,7 +36112,7 @@
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I585" t="inlineStr">
@@ -36173,7 +36173,7 @@
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I586" t="inlineStr">
@@ -36234,7 +36234,7 @@
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I587" t="inlineStr">
@@ -36295,7 +36295,7 @@
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I588" t="inlineStr">
@@ -36356,7 +36356,7 @@
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I589" t="inlineStr">
@@ -36417,7 +36417,7 @@
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I590" t="inlineStr">
@@ -36478,7 +36478,7 @@
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I591" t="inlineStr">
@@ -36539,7 +36539,7 @@
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I592" t="inlineStr">
@@ -36600,7 +36600,7 @@
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I593" t="inlineStr">
@@ -36661,7 +36661,7 @@
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I594" t="inlineStr">
@@ -36722,7 +36722,7 @@
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I595" t="inlineStr">
@@ -36783,7 +36783,7 @@
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I596" t="inlineStr">
@@ -36844,7 +36844,7 @@
       </c>
       <c r="H597" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I597" t="inlineStr">
@@ -36905,7 +36905,7 @@
       </c>
       <c r="H598" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I598" t="inlineStr">
@@ -36966,7 +36966,7 @@
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I599" t="inlineStr">
@@ -37027,7 +37027,7 @@
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I600" t="inlineStr">
@@ -37088,7 +37088,7 @@
       </c>
       <c r="H601" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I601" t="inlineStr">
@@ -37149,7 +37149,7 @@
       </c>
       <c r="H602" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I602" t="inlineStr">
@@ -37210,7 +37210,7 @@
       </c>
       <c r="H603" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I603" t="inlineStr">
@@ -37271,7 +37271,7 @@
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I604" t="inlineStr">
@@ -37332,7 +37332,7 @@
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I605" t="inlineStr">
@@ -37393,7 +37393,7 @@
       </c>
       <c r="H606" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I606" t="inlineStr">
@@ -37454,7 +37454,7 @@
       </c>
       <c r="H607" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I607" t="inlineStr">
@@ -37515,7 +37515,7 @@
       </c>
       <c r="H608" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I608" t="inlineStr">
@@ -37576,7 +37576,7 @@
       </c>
       <c r="H609" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I609" t="inlineStr">
@@ -37637,7 +37637,7 @@
       </c>
       <c r="H610" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I610" t="inlineStr">
@@ -37698,7 +37698,7 @@
       </c>
       <c r="H611" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I611" t="inlineStr">
@@ -37759,7 +37759,7 @@
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I612" t="inlineStr">
@@ -37820,7 +37820,7 @@
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I613" t="inlineStr">
@@ -37881,7 +37881,7 @@
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I614" t="inlineStr">
@@ -37942,7 +37942,7 @@
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I615" t="inlineStr">
@@ -38003,7 +38003,7 @@
       </c>
       <c r="H616" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I616" t="inlineStr">
@@ -38064,7 +38064,7 @@
       </c>
       <c r="H617" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I617" t="inlineStr">
@@ -38125,7 +38125,7 @@
       </c>
       <c r="H618" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I618" t="inlineStr">
@@ -38186,7 +38186,7 @@
       </c>
       <c r="H619" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I619" t="inlineStr">
@@ -38247,7 +38247,7 @@
       </c>
       <c r="H620" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I620" t="inlineStr">
@@ -38308,7 +38308,7 @@
       </c>
       <c r="H621" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I621" t="inlineStr">
@@ -38369,7 +38369,7 @@
       </c>
       <c r="H622" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I622" t="inlineStr">
@@ -38430,7 +38430,7 @@
       </c>
       <c r="H623" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I623" t="inlineStr">
@@ -38491,7 +38491,7 @@
       </c>
       <c r="H624" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I624" t="inlineStr">
@@ -38552,7 +38552,7 @@
       </c>
       <c r="H625" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I625" t="inlineStr">
@@ -38613,7 +38613,7 @@
       </c>
       <c r="H626" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I626" t="inlineStr">
@@ -38674,7 +38674,7 @@
       </c>
       <c r="H627" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I627" t="inlineStr">
@@ -38735,7 +38735,7 @@
       </c>
       <c r="H628" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I628" t="inlineStr">
@@ -38796,7 +38796,7 @@
       </c>
       <c r="H629" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I629" t="inlineStr">
@@ -38857,7 +38857,7 @@
       </c>
       <c r="H630" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I630" t="inlineStr">
@@ -38918,7 +38918,7 @@
       </c>
       <c r="H631" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I631" t="inlineStr">
@@ -38979,7 +38979,7 @@
       </c>
       <c r="H632" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I632" t="inlineStr">
@@ -39040,7 +39040,7 @@
       </c>
       <c r="H633" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I633" t="inlineStr">
@@ -39101,7 +39101,7 @@
       </c>
       <c r="H634" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I634" t="inlineStr">
@@ -39162,7 +39162,7 @@
       </c>
       <c r="H635" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I635" t="inlineStr">
@@ -39284,7 +39284,7 @@
       </c>
       <c r="H637" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I637" t="inlineStr">
@@ -39345,7 +39345,7 @@
       </c>
       <c r="H638" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I638" t="inlineStr">
@@ -39406,7 +39406,7 @@
       </c>
       <c r="H639" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I639" t="inlineStr">
@@ -39467,7 +39467,7 @@
       </c>
       <c r="H640" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I640" t="inlineStr">
@@ -39528,7 +39528,7 @@
       </c>
       <c r="H641" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I641" t="inlineStr">
@@ -39589,7 +39589,7 @@
       </c>
       <c r="H642" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I642" t="inlineStr">
@@ -39650,7 +39650,7 @@
       </c>
       <c r="H643" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I643" t="inlineStr">
@@ -39711,7 +39711,7 @@
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I644" t="inlineStr">
@@ -39772,7 +39772,7 @@
       </c>
       <c r="H645" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I645" t="inlineStr">
@@ -39894,7 +39894,7 @@
       </c>
       <c r="H647" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I647" t="inlineStr">
@@ -39955,7 +39955,7 @@
       </c>
       <c r="H648" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I648" t="inlineStr">
@@ -40016,7 +40016,7 @@
       </c>
       <c r="H649" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I649" t="inlineStr">
@@ -40077,7 +40077,7 @@
       </c>
       <c r="H650" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I650" t="inlineStr">
@@ -40199,7 +40199,7 @@
       </c>
       <c r="H652" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I652" t="inlineStr">
@@ -40260,7 +40260,7 @@
       </c>
       <c r="H653" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I653" t="inlineStr">
@@ -40321,7 +40321,7 @@
       </c>
       <c r="H654" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I654" t="inlineStr">
@@ -40382,7 +40382,7 @@
       </c>
       <c r="H655" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I655" t="inlineStr">
@@ -40443,7 +40443,7 @@
       </c>
       <c r="H656" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I656" t="inlineStr">
@@ -40504,7 +40504,7 @@
       </c>
       <c r="H657" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I657" t="inlineStr">
@@ -40565,7 +40565,7 @@
       </c>
       <c r="H658" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I658" t="inlineStr">
@@ -40687,7 +40687,7 @@
       </c>
       <c r="H660" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I660" t="inlineStr">
@@ -40748,7 +40748,7 @@
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I661" t="inlineStr">
@@ -40809,7 +40809,7 @@
       </c>
       <c r="H662" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I662" t="inlineStr">
@@ -40870,7 +40870,7 @@
       </c>
       <c r="H663" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I663" t="inlineStr">
@@ -40931,7 +40931,7 @@
       </c>
       <c r="H664" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I664" t="inlineStr">
@@ -40992,7 +40992,7 @@
       </c>
       <c r="H665" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I665" t="inlineStr">
@@ -41053,7 +41053,7 @@
       </c>
       <c r="H666" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I666" t="inlineStr">
@@ -41114,7 +41114,7 @@
       </c>
       <c r="H667" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I667" t="inlineStr">
@@ -41175,7 +41175,7 @@
       </c>
       <c r="H668" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I668" t="inlineStr">
@@ -41236,7 +41236,7 @@
       </c>
       <c r="H669" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I669" t="inlineStr">
@@ -41297,7 +41297,7 @@
       </c>
       <c r="H670" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I670" t="inlineStr">
@@ -41358,7 +41358,7 @@
       </c>
       <c r="H671" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I671" t="inlineStr">
@@ -41419,7 +41419,7 @@
       </c>
       <c r="H672" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I672" t="inlineStr">
@@ -41541,7 +41541,7 @@
       </c>
       <c r="H674" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I674" t="inlineStr">
@@ -41602,7 +41602,7 @@
       </c>
       <c r="H675" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I675" t="inlineStr">
@@ -41663,7 +41663,7 @@
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I676" t="inlineStr">
@@ -41724,7 +41724,7 @@
       </c>
       <c r="H677" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I677" t="inlineStr">
@@ -41785,7 +41785,7 @@
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I678" t="inlineStr">
@@ -41846,7 +41846,7 @@
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I679" t="inlineStr">
@@ -41907,7 +41907,7 @@
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I680" t="inlineStr">
@@ -41968,7 +41968,7 @@
       </c>
       <c r="H681" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I681" t="inlineStr">
@@ -42029,7 +42029,7 @@
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I682" t="inlineStr">
@@ -42090,7 +42090,7 @@
       </c>
       <c r="H683" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I683" t="inlineStr">
@@ -42151,7 +42151,7 @@
       </c>
       <c r="H684" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I684" t="inlineStr">
@@ -42212,7 +42212,7 @@
       </c>
       <c r="H685" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I685" t="inlineStr">
@@ -42273,7 +42273,7 @@
       </c>
       <c r="H686" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I686" t="inlineStr">
@@ -42395,7 +42395,7 @@
       </c>
       <c r="H688" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I688" t="inlineStr">
@@ -42456,7 +42456,7 @@
       </c>
       <c r="H689" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I689" t="inlineStr">
@@ -42517,7 +42517,7 @@
       </c>
       <c r="H690" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I690" t="inlineStr">
@@ -42639,7 +42639,7 @@
       </c>
       <c r="H692" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I692" t="inlineStr">
@@ -42700,7 +42700,7 @@
       </c>
       <c r="H693" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I693" t="inlineStr">
@@ -42761,7 +42761,7 @@
       </c>
       <c r="H694" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I694" t="inlineStr">
@@ -42822,7 +42822,7 @@
       </c>
       <c r="H695" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I695" t="inlineStr">
@@ -42883,7 +42883,7 @@
       </c>
       <c r="H696" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I696" t="inlineStr">
@@ -42944,7 +42944,7 @@
       </c>
       <c r="H697" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I697" t="inlineStr">
@@ -43005,7 +43005,7 @@
       </c>
       <c r="H698" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I698" t="inlineStr">
@@ -43066,7 +43066,7 @@
       </c>
       <c r="H699" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I699" t="inlineStr">
@@ -43127,7 +43127,7 @@
       </c>
       <c r="H700" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I700" t="inlineStr">
@@ -43188,7 +43188,7 @@
       </c>
       <c r="H701" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I701" t="inlineStr">
@@ -43249,7 +43249,7 @@
       </c>
       <c r="H702" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I702" t="inlineStr">
@@ -43371,7 +43371,7 @@
       </c>
       <c r="H704" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I704" t="inlineStr">
@@ -43432,7 +43432,7 @@
       </c>
       <c r="H705" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I705" t="inlineStr">
@@ -43493,7 +43493,7 @@
       </c>
       <c r="H706" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I706" t="inlineStr">
@@ -43554,7 +43554,7 @@
       </c>
       <c r="H707" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I707" t="inlineStr">
@@ -43615,7 +43615,7 @@
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I708" t="inlineStr">
@@ -43676,7 +43676,7 @@
       </c>
       <c r="H709" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I709" t="inlineStr">
@@ -43737,7 +43737,7 @@
       </c>
       <c r="H710" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I710" t="inlineStr">
@@ -43798,7 +43798,7 @@
       </c>
       <c r="H711" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I711" t="inlineStr">
@@ -43859,7 +43859,7 @@
       </c>
       <c r="H712" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I712" t="inlineStr">
@@ -43920,7 +43920,7 @@
       </c>
       <c r="H713" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I713" t="inlineStr">
@@ -43981,7 +43981,7 @@
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I714" t="inlineStr">
@@ -44042,7 +44042,7 @@
       </c>
       <c r="H715" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I715" t="inlineStr">
@@ -44164,7 +44164,7 @@
       </c>
       <c r="H717" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I717" t="inlineStr">
@@ -44225,7 +44225,7 @@
       </c>
       <c r="H718" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I718" t="inlineStr">
@@ -44286,7 +44286,7 @@
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I719" t="inlineStr">
@@ -44347,7 +44347,7 @@
       </c>
       <c r="H720" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I720" t="inlineStr">
@@ -44408,7 +44408,7 @@
       </c>
       <c r="H721" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I721" t="inlineStr">
@@ -44469,7 +44469,7 @@
       </c>
       <c r="H722" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I722" t="inlineStr">
@@ -44591,7 +44591,7 @@
       </c>
       <c r="H724" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I724" t="inlineStr">
@@ -44652,7 +44652,7 @@
       </c>
       <c r="H725" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I725" t="inlineStr">
@@ -44713,7 +44713,7 @@
       </c>
       <c r="H726" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I726" t="inlineStr">
@@ -44774,7 +44774,7 @@
       </c>
       <c r="H727" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I727" t="inlineStr">
@@ -44835,7 +44835,7 @@
       </c>
       <c r="H728" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I728" t="inlineStr">
@@ -44896,7 +44896,7 @@
       </c>
       <c r="H729" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I729" t="inlineStr">
@@ -45018,7 +45018,7 @@
       </c>
       <c r="H731" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I731" t="inlineStr">
@@ -45079,7 +45079,7 @@
       </c>
       <c r="H732" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I732" t="inlineStr">
@@ -45140,7 +45140,7 @@
       </c>
       <c r="H733" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I733" t="inlineStr">
@@ -45201,7 +45201,7 @@
       </c>
       <c r="H734" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I734" t="inlineStr">
@@ -45323,7 +45323,7 @@
       </c>
       <c r="H736" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I736" t="inlineStr">
@@ -45384,7 +45384,7 @@
       </c>
       <c r="H737" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I737" t="inlineStr">
@@ -45445,7 +45445,7 @@
       </c>
       <c r="H738" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I738" t="inlineStr">
@@ -45506,7 +45506,7 @@
       </c>
       <c r="H739" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I739" t="inlineStr">
@@ -45567,7 +45567,7 @@
       </c>
       <c r="H740" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I740" t="inlineStr">
@@ -45628,7 +45628,7 @@
       </c>
       <c r="H741" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I741" t="inlineStr">
@@ -45689,7 +45689,7 @@
       </c>
       <c r="H742" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I742" t="inlineStr">
@@ -45750,7 +45750,7 @@
       </c>
       <c r="H743" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I743" t="inlineStr">
@@ -45811,7 +45811,7 @@
       </c>
       <c r="H744" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I744" t="inlineStr">
@@ -45933,7 +45933,7 @@
       </c>
       <c r="H746" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I746" t="inlineStr">
@@ -45994,7 +45994,7 @@
       </c>
       <c r="H747" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I747" t="inlineStr">
@@ -46055,7 +46055,7 @@
       </c>
       <c r="H748" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I748" t="inlineStr">
@@ -46116,7 +46116,7 @@
       </c>
       <c r="H749" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I749" t="inlineStr">
@@ -46177,7 +46177,7 @@
       </c>
       <c r="H750" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I750" t="inlineStr">
@@ -46238,7 +46238,7 @@
       </c>
       <c r="H751" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I751" t="inlineStr">
@@ -46299,7 +46299,7 @@
       </c>
       <c r="H752" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I752" t="inlineStr">
@@ -46360,7 +46360,7 @@
       </c>
       <c r="H753" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I753" t="inlineStr">
@@ -46421,7 +46421,7 @@
       </c>
       <c r="H754" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I754" t="inlineStr">
@@ -46482,7 +46482,7 @@
       </c>
       <c r="H755" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I755" t="inlineStr">
@@ -46543,7 +46543,7 @@
       </c>
       <c r="H756" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I756" t="inlineStr">
@@ -46604,7 +46604,7 @@
       </c>
       <c r="H757" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I757" t="inlineStr">
@@ -46665,7 +46665,7 @@
       </c>
       <c r="H758" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I758" t="inlineStr">
@@ -46787,7 +46787,7 @@
       </c>
       <c r="H760" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I760" t="inlineStr">
@@ -46848,7 +46848,7 @@
       </c>
       <c r="H761" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I761" t="inlineStr">
@@ -46909,7 +46909,7 @@
       </c>
       <c r="H762" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I762" t="inlineStr">
@@ -46970,7 +46970,7 @@
       </c>
       <c r="H763" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I763" t="inlineStr">
@@ -47031,7 +47031,7 @@
       </c>
       <c r="H764" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I764" t="inlineStr">
@@ -47092,7 +47092,7 @@
       </c>
       <c r="H765" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I765" t="inlineStr">
@@ -47153,7 +47153,7 @@
       </c>
       <c r="H766" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I766" t="inlineStr">
@@ -47214,7 +47214,7 @@
       </c>
       <c r="H767" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I767" t="inlineStr">
@@ -47275,7 +47275,7 @@
       </c>
       <c r="H768" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I768" t="inlineStr">
@@ -47336,7 +47336,7 @@
       </c>
       <c r="H769" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I769" t="inlineStr">
@@ -47397,7 +47397,7 @@
       </c>
       <c r="H770" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I770" t="inlineStr">
@@ -47458,7 +47458,7 @@
       </c>
       <c r="H771" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I771" t="inlineStr">
@@ -47519,7 +47519,7 @@
       </c>
       <c r="H772" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I772" t="inlineStr">
@@ -47580,7 +47580,7 @@
       </c>
       <c r="H773" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I773" t="inlineStr">
@@ -47641,7 +47641,7 @@
       </c>
       <c r="H774" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I774" t="inlineStr">
@@ -47702,7 +47702,7 @@
       </c>
       <c r="H775" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I775" t="inlineStr">
@@ -47763,7 +47763,7 @@
       </c>
       <c r="H776" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I776" t="inlineStr">
@@ -47824,7 +47824,7 @@
       </c>
       <c r="H777" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I777" t="inlineStr">
@@ -47885,7 +47885,7 @@
       </c>
       <c r="H778" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I778" t="inlineStr">
@@ -47946,7 +47946,7 @@
       </c>
       <c r="H779" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I779" t="inlineStr">
@@ -48007,7 +48007,7 @@
       </c>
       <c r="H780" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I780" t="inlineStr">
@@ -48068,7 +48068,7 @@
       </c>
       <c r="H781" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I781" t="inlineStr">
@@ -48129,7 +48129,7 @@
       </c>
       <c r="H782" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I782" t="inlineStr">
@@ -48190,7 +48190,7 @@
       </c>
       <c r="H783" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I783" t="inlineStr">
@@ -48251,7 +48251,7 @@
       </c>
       <c r="H784" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I784" t="inlineStr">
@@ -48312,7 +48312,7 @@
       </c>
       <c r="H785" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I785" t="inlineStr">
@@ -48434,7 +48434,7 @@
       </c>
       <c r="H787" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I787" t="inlineStr">
@@ -48556,7 +48556,7 @@
       </c>
       <c r="H789" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I789" t="inlineStr">
@@ -48617,7 +48617,7 @@
       </c>
       <c r="H790" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I790" t="inlineStr">
@@ -48678,7 +48678,7 @@
       </c>
       <c r="H791" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I791" t="inlineStr">
@@ -48739,7 +48739,7 @@
       </c>
       <c r="H792" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I792" t="inlineStr">
@@ -48800,7 +48800,7 @@
       </c>
       <c r="H793" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I793" t="inlineStr">
@@ -48861,7 +48861,7 @@
       </c>
       <c r="H794" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I794" t="inlineStr">
@@ -48922,7 +48922,7 @@
       </c>
       <c r="H795" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I795" t="inlineStr">
@@ -48983,7 +48983,7 @@
       </c>
       <c r="H796" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I796" t="inlineStr">
@@ -49044,7 +49044,7 @@
       </c>
       <c r="H797" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I797" t="inlineStr">
@@ -49105,7 +49105,7 @@
       </c>
       <c r="H798" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I798" t="inlineStr">
@@ -49166,7 +49166,7 @@
       </c>
       <c r="H799" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I799" t="inlineStr">
@@ -49227,7 +49227,7 @@
       </c>
       <c r="H800" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I800" t="inlineStr">
@@ -49288,7 +49288,7 @@
       </c>
       <c r="H801" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I801" t="inlineStr">
@@ -49349,7 +49349,7 @@
       </c>
       <c r="H802" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I802" t="inlineStr">
@@ -49410,7 +49410,7 @@
       </c>
       <c r="H803" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I803" t="inlineStr">
@@ -49471,7 +49471,7 @@
       </c>
       <c r="H804" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I804" t="inlineStr">
@@ -49532,7 +49532,7 @@
       </c>
       <c r="H805" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I805" t="inlineStr">
@@ -49593,7 +49593,7 @@
       </c>
       <c r="H806" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I806" t="inlineStr">
@@ -49654,7 +49654,7 @@
       </c>
       <c r="H807" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I807" t="inlineStr">
@@ -49715,7 +49715,7 @@
       </c>
       <c r="H808" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I808" t="inlineStr">
@@ -49776,7 +49776,7 @@
       </c>
       <c r="H809" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I809" t="inlineStr">
@@ -49837,7 +49837,7 @@
       </c>
       <c r="H810" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I810" t="inlineStr">
@@ -49898,7 +49898,7 @@
       </c>
       <c r="H811" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I811" t="inlineStr">
@@ -49959,7 +49959,7 @@
       </c>
       <c r="H812" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I812" t="inlineStr">
@@ -50020,7 +50020,7 @@
       </c>
       <c r="H813" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I813" t="inlineStr">
@@ -50081,7 +50081,7 @@
       </c>
       <c r="H814" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I814" t="inlineStr">
@@ -50142,7 +50142,7 @@
       </c>
       <c r="H815" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I815" t="inlineStr">
@@ -50264,7 +50264,7 @@
       </c>
       <c r="H817" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I817" t="inlineStr">
@@ -50325,7 +50325,7 @@
       </c>
       <c r="H818" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I818" t="inlineStr">
@@ -50386,7 +50386,7 @@
       </c>
       <c r="H819" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I819" t="inlineStr">
@@ -50447,7 +50447,7 @@
       </c>
       <c r="H820" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I820" t="inlineStr">
@@ -50508,7 +50508,7 @@
       </c>
       <c r="H821" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I821" t="inlineStr">
@@ -50630,7 +50630,7 @@
       </c>
       <c r="H823" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I823" t="inlineStr">
@@ -50691,7 +50691,7 @@
       </c>
       <c r="H824" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I824" t="inlineStr">
@@ -50752,7 +50752,7 @@
       </c>
       <c r="H825" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I825" t="inlineStr">
@@ -50813,7 +50813,7 @@
       </c>
       <c r="H826" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I826" t="inlineStr">
@@ -50874,7 +50874,7 @@
       </c>
       <c r="H827" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I827" t="inlineStr">
@@ -50935,7 +50935,7 @@
       </c>
       <c r="H828" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I828" t="inlineStr">
@@ -50996,7 +50996,7 @@
       </c>
       <c r="H829" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I829" t="inlineStr">
@@ -51118,7 +51118,7 @@
       </c>
       <c r="H831" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I831" t="inlineStr">
@@ -51179,7 +51179,7 @@
       </c>
       <c r="H832" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I832" t="inlineStr">
@@ -51240,7 +51240,7 @@
       </c>
       <c r="H833" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I833" t="inlineStr">
@@ -51301,7 +51301,7 @@
       </c>
       <c r="H834" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I834" t="inlineStr">
@@ -51362,7 +51362,7 @@
       </c>
       <c r="H835" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I835" t="inlineStr">
@@ -51423,7 +51423,7 @@
       </c>
       <c r="H836" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I836" t="inlineStr">
@@ -51484,7 +51484,7 @@
       </c>
       <c r="H837" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I837" t="inlineStr">
@@ -51545,7 +51545,7 @@
       </c>
       <c r="H838" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I838" t="inlineStr">
@@ -51606,7 +51606,7 @@
       </c>
       <c r="H839" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I839" t="inlineStr">
@@ -51667,7 +51667,7 @@
       </c>
       <c r="H840" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I840" t="inlineStr">
@@ -51728,7 +51728,7 @@
       </c>
       <c r="H841" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I841" t="inlineStr">
@@ -51789,7 +51789,7 @@
       </c>
       <c r="H842" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I842" t="inlineStr">
@@ -51850,7 +51850,7 @@
       </c>
       <c r="H843" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I843" t="inlineStr">
@@ -51911,7 +51911,7 @@
       </c>
       <c r="H844" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I844" t="inlineStr">
@@ -51972,7 +51972,7 @@
       </c>
       <c r="H845" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I845" t="inlineStr">
@@ -52033,7 +52033,7 @@
       </c>
       <c r="H846" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I846" t="inlineStr">
@@ -52094,7 +52094,7 @@
       </c>
       <c r="H847" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I847" t="inlineStr">

--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/ene-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/ene-2025.xlsx
@@ -669,11 +669,7 @@
           <t>SERVICIO DE SALUD SUR HOSPITAL EXEQUIEL</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>DIMERC S A</t>
@@ -727,7 +723,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1645,11 +1641,7 @@
           <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Los Ríos</t>
-        </is>
-      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>MARYUN Seguridad Industrial</t>
@@ -1950,11 +1942,7 @@
           <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>GRUPO DK SERVICIOS LIMITADA</t>
@@ -2133,11 +2121,7 @@
           <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>COMERCIAL AGUSTIN LIMITADA</t>
@@ -2621,11 +2605,7 @@
           <t>SERVICIO SALUD OCCIDENTE HOSPITAL DR FELIX BULNES CERDA</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
@@ -2743,11 +2723,7 @@
           <t>I MUNICIPALIDAD DE LIMACHE</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>DISTRIBUIDORA MANZANO S A</t>
@@ -3231,11 +3207,7 @@
           <t>Corporación Municipal de Deportes de Ñuñoa</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>WINKLER LIMITADA</t>
@@ -4207,11 +4179,7 @@
           <t>SERVICIO SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>DIMERC S A</t>
@@ -6634,7 +6602,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -6891,11 +6859,7 @@
           <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr">
         <is>
           <t>SCANNO SPA</t>
@@ -8172,11 +8136,7 @@
           <t>I MUNICIPALIDAD DE TOME</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Biobío</t>
-        </is>
-      </c>
+      <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
           <t>COMERCIAL MUNOZ Y COMPANIA LIMITADA</t>
@@ -8477,11 +8437,7 @@
           <t>SERVICIO NACIONAL ARAUCANIA SUR HOSPITAL DR ABRAHAM GODOY PENA LAUTARO</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+      <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
           <t>COMERCIALIZADORA PRANDELLI LIMITADA</t>
@@ -9084,7 +9040,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9145,7 +9101,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9270,11 +9226,7 @@
           <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Atacama</t>
-        </is>
-      </c>
+      <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr">
         <is>
           <t>DIMERC S A</t>
@@ -9501,7 +9453,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -9514,11 +9466,7 @@
           <t>UNIVERSIDAD METROPOLITANA DE CIENCIAS DE LA EDUCACION</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+      <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr">
         <is>
           <t>Marco Antonio</t>
@@ -9562,7 +9510,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -10856,11 +10804,7 @@
           <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+      <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr">
         <is>
           <t>PROVEEDORES INTEGRALES PRISA S A</t>
@@ -10975,7 +10919,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11283,11 +11227,7 @@
           <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
+      <c r="H178" t="inlineStr"/>
       <c r="I178" t="inlineStr">
         <is>
           <t>WINKLER LIMITADA</t>
@@ -11466,11 +11406,7 @@
           <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+      <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr">
         <is>
           <t>DISTRIBUIDORA MANZANO S A</t>
@@ -14333,11 +14269,7 @@
           <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>Los Lagos</t>
-        </is>
-      </c>
+      <c r="H228" t="inlineStr"/>
       <c r="I228" t="inlineStr">
         <is>
           <t>DIMERC S A</t>
@@ -14699,11 +14631,7 @@
           <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
-      <c r="H234" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+      <c r="H234" t="inlineStr"/>
       <c r="I234" t="inlineStr">
         <is>
           <t>DIMERC S A</t>
@@ -14760,11 +14688,7 @@
           <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
-      <c r="H235" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+      <c r="H235" t="inlineStr"/>
       <c r="I235" t="inlineStr">
         <is>
           <t>DIMERC S A</t>
@@ -15550,7 +15474,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -16041,11 +15965,7 @@
           <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE LAJA</t>
         </is>
       </c>
-      <c r="H256" t="inlineStr">
-        <is>
-          <t>Biobío</t>
-        </is>
-      </c>
+      <c r="H256" t="inlineStr"/>
       <c r="I256" t="inlineStr">
         <is>
           <t>DIMERC S A</t>
@@ -16346,11 +16266,7 @@
           <t>SERVICIO DE SALUD OCCIDENTE HOSPITAL SAN JUAN DE DIOS</t>
         </is>
       </c>
-      <c r="H261" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+      <c r="H261" t="inlineStr"/>
       <c r="I261" t="inlineStr">
         <is>
           <t>PROVEEDORES INTEGRALES PRISA S A</t>
@@ -16590,11 +16506,7 @@
           <t>HOSPITAL BASE OSORNO</t>
         </is>
       </c>
-      <c r="H265" t="inlineStr">
-        <is>
-          <t>Los Lagos</t>
-        </is>
-      </c>
+      <c r="H265" t="inlineStr"/>
       <c r="I265" t="inlineStr">
         <is>
           <t>MARYUN Seguridad Industrial</t>
@@ -16651,11 +16563,7 @@
           <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
-      <c r="H266" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+      <c r="H266" t="inlineStr"/>
       <c r="I266" t="inlineStr">
         <is>
           <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
@@ -16773,11 +16681,7 @@
           <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
-      <c r="H268" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+      <c r="H268" t="inlineStr"/>
       <c r="I268" t="inlineStr">
         <is>
           <t>DIMERC S A</t>
@@ -17261,11 +17165,7 @@
           <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
-      <c r="H276" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+      <c r="H276" t="inlineStr"/>
       <c r="I276" t="inlineStr">
         <is>
           <t>PROVEEDORES INTEGRALES PRISA S A</t>
@@ -18237,11 +18137,7 @@
           <t>HOSPITAL DE QUILPUE</t>
         </is>
       </c>
-      <c r="H292" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+      <c r="H292" t="inlineStr"/>
       <c r="I292" t="inlineStr">
         <is>
           <t>DIMERC S A</t>
@@ -18417,14 +18313,10 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
-        </is>
-      </c>
-      <c r="H295" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr"/>
       <c r="I295" t="inlineStr">
         <is>
           <t>SCANNO SPA</t>
@@ -18905,7 +18797,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -18969,11 +18861,7 @@
           <t>SERVICIO DE SALUD OCCIDENTE INSTITUTO TRAUMATOLOGICO DE SANTIAGO</t>
         </is>
       </c>
-      <c r="H304" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+      <c r="H304" t="inlineStr"/>
       <c r="I304" t="inlineStr">
         <is>
           <t>COMERCIALIZADORA VYB</t>
@@ -19152,11 +19040,7 @@
           <t>SERVICIO DE SALUD BIO BIO HOSPITAL SANTA BARBARA</t>
         </is>
       </c>
-      <c r="H307" t="inlineStr">
-        <is>
-          <t>Biobío</t>
-        </is>
-      </c>
+      <c r="H307" t="inlineStr"/>
       <c r="I307" t="inlineStr">
         <is>
           <t>COMERCIAL AGUSTIN LIMITADA</t>
@@ -19274,11 +19158,7 @@
           <t>SERVICIO NACIONAL ARAUCANIA SUR HOSPITAL DR ABRAHAM GODOY PENA LAUTARO</t>
         </is>
       </c>
-      <c r="H309" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+      <c r="H309" t="inlineStr"/>
       <c r="I309" t="inlineStr">
         <is>
           <t>prodesa</t>
@@ -20677,11 +20557,7 @@
           <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
-      <c r="H332" t="inlineStr">
-        <is>
-          <t>Los Lagos</t>
-        </is>
-      </c>
+      <c r="H332" t="inlineStr"/>
       <c r="I332" t="inlineStr">
         <is>
           <t>DIMERC S A</t>
@@ -21958,11 +21834,7 @@
           <t>I MUNICIPALIDAD DE SAN FELIPE</t>
         </is>
       </c>
-      <c r="H353" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+      <c r="H353" t="inlineStr"/>
       <c r="I353" t="inlineStr">
         <is>
           <t>MULTI SAFE SPA</t>
@@ -22507,11 +22379,7 @@
           <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE T</t>
         </is>
       </c>
-      <c r="H362" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+      <c r="H362" t="inlineStr"/>
       <c r="I362" t="inlineStr">
         <is>
           <t>DIMERC S A</t>
@@ -23117,11 +22985,7 @@
           <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
-      <c r="H372" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+      <c r="H372" t="inlineStr"/>
       <c r="I372" t="inlineStr">
         <is>
           <t>DIMERC S A</t>
@@ -24520,11 +24384,7 @@
           <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
-      <c r="H395" t="inlineStr">
-        <is>
-          <t>Los Ríos</t>
-        </is>
-      </c>
+      <c r="H395" t="inlineStr"/>
       <c r="I395" t="inlineStr">
         <is>
           <t>SOC COMERCIAL CINTEC LIMITADA</t>
@@ -25069,11 +24929,7 @@
           <t>I MUNICIPALIDAD DE CONSTITUCION</t>
         </is>
       </c>
-      <c r="H404" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
+      <c r="H404" t="inlineStr"/>
       <c r="I404" t="inlineStr">
         <is>
           <t>COMERCIAL AGUSTIN LIMITADA</t>
@@ -25191,11 +25047,7 @@
           <t>I MUNICIPALIDAD DE PADRE HURTADO</t>
         </is>
       </c>
-      <c r="H406" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+      <c r="H406" t="inlineStr"/>
       <c r="I406" t="inlineStr">
         <is>
           <t>COMERCIAL AGUSTIN LIMITADA</t>
@@ -27445,7 +27297,7 @@
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H443" t="inlineStr">
@@ -27570,11 +27422,7 @@
           <t>I MUNICIPALIDAD DE LIMACHE</t>
         </is>
       </c>
-      <c r="H445" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+      <c r="H445" t="inlineStr"/>
       <c r="I445" t="inlineStr">
         <is>
           <t>MG PUBLICIDAD Y EVENTOS SPA</t>
@@ -27994,14 +27842,10 @@
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
-        </is>
-      </c>
-      <c r="H452" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr"/>
       <c r="I452" t="inlineStr">
         <is>
           <t>COMERCIALIZADORA VYB</t>
@@ -30071,11 +29915,7 @@
           <t>SERVICIO SALUD OCCIDENTE HOSPITAL DR FELIX BULNES CERDA</t>
         </is>
       </c>
-      <c r="H486" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+      <c r="H486" t="inlineStr"/>
       <c r="I486" t="inlineStr">
         <is>
           <t>COMERCIAL RED OFFICE LIMITADA</t>
@@ -30193,11 +30033,7 @@
           <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
-      <c r="H488" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
+      <c r="H488" t="inlineStr"/>
       <c r="I488" t="inlineStr">
         <is>
           <t>DIMERC S A</t>
@@ -30373,7 +30209,7 @@
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H491" t="inlineStr">
@@ -31471,7 +31307,7 @@
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H509" t="inlineStr">
@@ -32206,11 +32042,7 @@
           <t>HOSPITAL METROPOLITANO DE SANTIAGO</t>
         </is>
       </c>
-      <c r="H521" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+      <c r="H521" t="inlineStr"/>
       <c r="I521" t="inlineStr">
         <is>
           <t>MG PUBLICIDAD Y EVENTOS SPA</t>
@@ -32267,11 +32099,7 @@
           <t>CENTRO DE REFERENCIA DE SALUD DE MAIPU</t>
         </is>
       </c>
-      <c r="H522" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+      <c r="H522" t="inlineStr"/>
       <c r="I522" t="inlineStr">
         <is>
           <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
@@ -32572,11 +32400,7 @@
           <t>HOSPITAL METROPOLITANO DE SANTIAGO</t>
         </is>
       </c>
-      <c r="H527" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+      <c r="H527" t="inlineStr"/>
       <c r="I527" t="inlineStr">
         <is>
           <t>MG PUBLICIDAD Y EVENTOS SPA</t>
@@ -34219,11 +34043,7 @@
           <t>HOSPITAL DE QUILPUE</t>
         </is>
       </c>
-      <c r="H554" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+      <c r="H554" t="inlineStr"/>
       <c r="I554" t="inlineStr">
         <is>
           <t>DISTRIBUIDORA MANZANO S A</t>
@@ -34389,7 +34209,7 @@
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F557" t="inlineStr">
@@ -34829,11 +34649,7 @@
           <t>I MUNICIPALIDAD DE LA COMUNA DE EL BOSQUE</t>
         </is>
       </c>
-      <c r="H564" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+      <c r="H564" t="inlineStr"/>
       <c r="I564" t="inlineStr">
         <is>
           <t>DIMERC S A</t>
@@ -38184,11 +38000,7 @@
           <t>I MUNICIPALIDAD DE SAN FERNANDO</t>
         </is>
       </c>
-      <c r="H619" t="inlineStr">
-        <is>
-          <t>O'Higgins</t>
-        </is>
-      </c>
+      <c r="H619" t="inlineStr"/>
       <c r="I619" t="inlineStr">
         <is>
           <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
@@ -38608,7 +38420,7 @@
       </c>
       <c r="G626" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H626" t="inlineStr">
@@ -39221,11 +39033,7 @@
           <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
-      <c r="H636" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+      <c r="H636" t="inlineStr"/>
       <c r="I636" t="inlineStr">
         <is>
           <t>SCANNO SPA</t>
@@ -39452,7 +39260,7 @@
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F640" t="inlineStr">
@@ -39831,11 +39639,7 @@
           <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
-      <c r="H646" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+      <c r="H646" t="inlineStr"/>
       <c r="I646" t="inlineStr">
         <is>
           <t>DIMERC S A</t>
@@ -40136,11 +39940,7 @@
           <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
-      <c r="H651" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+      <c r="H651" t="inlineStr"/>
       <c r="I651" t="inlineStr">
         <is>
           <t>Barron Vieyra International Ltda.</t>
@@ -40560,7 +40360,7 @@
       </c>
       <c r="G658" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H658" t="inlineStr">
@@ -40624,11 +40424,7 @@
           <t>SERVICIO DE SALUD NUBLE HOSPITAL DE QUIRIHUE</t>
         </is>
       </c>
-      <c r="H659" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
+      <c r="H659" t="inlineStr"/>
       <c r="I659" t="inlineStr">
         <is>
           <t>SOLUCIONES INTEGRALES DE LIMPIEZA LIMITADA</t>
@@ -41478,11 +41274,7 @@
           <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
-      <c r="H673" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+      <c r="H673" t="inlineStr"/>
       <c r="I673" t="inlineStr">
         <is>
           <t>DISTRIBUIDORA MANZANO S A</t>
@@ -42085,7 +41877,7 @@
       </c>
       <c r="G683" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H683" t="inlineStr">
@@ -42332,11 +42124,7 @@
           <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
-      <c r="H687" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+      <c r="H687" t="inlineStr"/>
       <c r="I687" t="inlineStr">
         <is>
           <t>MG PUBLICIDAD Y EVENTOS SPA</t>
@@ -42576,11 +42364,7 @@
           <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
-      <c r="H691" t="inlineStr">
-        <is>
-          <t>Los Lagos</t>
-        </is>
-      </c>
+      <c r="H691" t="inlineStr"/>
       <c r="I691" t="inlineStr">
         <is>
           <t>PROVEEDORES INTEGRALES PRISA S A</t>
@@ -43308,11 +43092,7 @@
           <t>I MUNICIPALIDAD DE FUTRONO</t>
         </is>
       </c>
-      <c r="H703" t="inlineStr">
-        <is>
-          <t>Los Ríos</t>
-        </is>
-      </c>
+      <c r="H703" t="inlineStr"/>
       <c r="I703" t="inlineStr">
         <is>
           <t>PROVEEDORES INTEGRALES PRISA S A</t>
@@ -44037,7 +43817,7 @@
       </c>
       <c r="G715" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H715" t="inlineStr">
@@ -44098,14 +43878,10 @@
       </c>
       <c r="G716" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
-        </is>
-      </c>
-      <c r="H716" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
+        </is>
+      </c>
+      <c r="H716" t="inlineStr"/>
       <c r="I716" t="inlineStr">
         <is>
           <t>PROVEEDORES INTEGRALES PRISA S A</t>
@@ -44528,11 +44304,7 @@
           <t>SERVICIO DE SALUD ORIENTE HOSPITAL DEL SALVADOR</t>
         </is>
       </c>
-      <c r="H723" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+      <c r="H723" t="inlineStr"/>
       <c r="I723" t="inlineStr">
         <is>
           <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
@@ -44955,11 +44727,7 @@
           <t>HOSPITAL COMPLEJO ASISTENCIAL PADRE LAS CASAS</t>
         </is>
       </c>
-      <c r="H730" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+      <c r="H730" t="inlineStr"/>
       <c r="I730" t="inlineStr">
         <is>
           <t>PROVEEDORES INTEGRALES PRISA S A</t>
@@ -45260,11 +45028,7 @@
           <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
-      <c r="H735" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+      <c r="H735" t="inlineStr"/>
       <c r="I735" t="inlineStr">
         <is>
           <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
@@ -45870,11 +45634,7 @@
           <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
-      <c r="H745" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+      <c r="H745" t="inlineStr"/>
       <c r="I745" t="inlineStr">
         <is>
           <t>PROVEEDORES INTEGRALES DEL SUR S.A.</t>
@@ -46724,11 +46484,7 @@
           <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
-      <c r="H759" t="inlineStr">
-        <is>
-          <t>Coquimbo</t>
-        </is>
-      </c>
+      <c r="H759" t="inlineStr"/>
       <c r="I759" t="inlineStr">
         <is>
           <t>DIMERC S A</t>
@@ -46965,7 +46721,7 @@
       </c>
       <c r="G763" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H763" t="inlineStr">
@@ -48371,11 +48127,7 @@
           <t>INSTITUTO NACIONAL DEL TORAX</t>
         </is>
       </c>
-      <c r="H786" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+      <c r="H786" t="inlineStr"/>
       <c r="I786" t="inlineStr">
         <is>
           <t>PROVEEDORES INTEGRALES PRISA S A</t>
@@ -48493,11 +48245,7 @@
           <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
-      <c r="H788" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+      <c r="H788" t="inlineStr"/>
       <c r="I788" t="inlineStr">
         <is>
           <t>PROVEEDORES INTEGRALES PRISA S A</t>
@@ -48917,7 +48665,7 @@
       </c>
       <c r="G795" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H795" t="inlineStr">
@@ -49334,7 +49082,7 @@
       </c>
       <c r="E802" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F802" t="inlineStr">
@@ -50201,11 +49949,7 @@
           <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
-      <c r="H816" t="inlineStr">
-        <is>
-          <t>Los Lagos</t>
-        </is>
-      </c>
+      <c r="H816" t="inlineStr"/>
       <c r="I816" t="inlineStr">
         <is>
           <t>PROVEEDORES INTEGRALES PRISA S A</t>
@@ -50567,11 +50311,7 @@
           <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
-      <c r="H822" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+      <c r="H822" t="inlineStr"/>
       <c r="I822" t="inlineStr">
         <is>
           <t>DIMERC S A</t>
@@ -51055,11 +50795,7 @@
           <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
-      <c r="H830" t="inlineStr">
-        <is>
-          <t>Los Lagos</t>
-        </is>
-      </c>
+      <c r="H830" t="inlineStr"/>
       <c r="I830" t="inlineStr">
         <is>
           <t>SOC COMERCIAL CINTEC LIMITADA</t>

--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/ene-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/ene-2025.xlsx
@@ -562,7 +562,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -680,7 +688,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -802,7 +814,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -924,7 +940,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -985,7 +1005,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1046,7 +1070,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1107,7 +1135,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1168,7 +1200,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1229,7 +1265,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1290,7 +1330,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1595,7 +1639,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1713,7 +1761,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1774,7 +1826,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1835,7 +1891,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1896,7 +1956,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1953,7 +2017,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2498,7 +2566,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2559,7 +2631,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2795,7 +2871,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2856,7 +2936,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2978,7 +3062,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3100,7 +3188,11 @@
           <t>76.525.922-3</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3161,7 +3253,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3218,7 +3314,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3340,7 +3440,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3401,7 +3505,11 @@
           <t>77.173.807-9</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3584,7 +3692,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3645,7 +3757,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3706,7 +3822,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3767,7 +3887,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3889,7 +4013,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4011,7 +4139,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4133,7 +4265,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4190,7 +4326,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4251,7 +4391,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4312,7 +4456,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4373,7 +4521,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4434,7 +4586,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4495,7 +4651,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4678,7 +4838,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4739,7 +4903,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4800,7 +4968,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4922,7 +5094,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4983,7 +5159,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5105,7 +5285,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5227,7 +5411,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5288,7 +5476,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5410,7 +5602,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5593,7 +5789,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5715,7 +5915,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5837,7 +6041,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5959,7 +6167,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6020,7 +6232,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6081,7 +6297,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6142,7 +6362,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6508,7 +6732,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6569,7 +6797,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6630,7 +6862,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6752,7 +6988,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6813,7 +7053,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6992,7 +7236,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7053,7 +7301,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7175,7 +7427,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7358,7 +7614,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7541,7 +7801,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7602,7 +7866,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7663,7 +7931,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7724,7 +7996,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7846,7 +8122,11 @@
           <t>76.100.933-8</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8029,7 +8309,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8090,7 +8374,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8147,7 +8435,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8208,7 +8500,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8269,7 +8565,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8391,7 +8691,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8509,7 +8813,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8570,7 +8878,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8631,7 +8943,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8753,7 +9069,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8814,7 +9134,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8875,7 +9199,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9058,7 +9386,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9180,7 +9512,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9237,7 +9573,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9298,7 +9638,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9599,7 +9943,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9660,7 +10008,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9721,7 +10073,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9782,7 +10138,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9843,7 +10203,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9904,7 +10268,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10209,7 +10577,11 @@
           <t>76.525.922-3</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10331,7 +10703,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10575,7 +10951,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10636,7 +11016,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10697,7 +11081,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10815,7 +11203,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10937,7 +11329,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11238,7 +11634,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11299,7 +11699,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11360,7 +11764,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11478,7 +11886,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11722,7 +12134,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11783,7 +12199,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11905,7 +12325,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11966,7 +12390,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12027,7 +12455,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12332,7 +12764,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12393,7 +12829,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12454,7 +12894,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12576,7 +13020,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12637,7 +13085,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12698,7 +13150,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12881,7 +13337,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12942,7 +13402,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13003,7 +13467,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13064,7 +13532,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13125,7 +13597,11 @@
           <t>77.623.039-1</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13186,7 +13662,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13247,7 +13727,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13369,7 +13853,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13430,7 +13918,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13491,7 +13983,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13552,7 +14048,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13613,7 +14113,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13674,7 +14178,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13735,7 +14243,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13796,7 +14308,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13857,7 +14373,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13918,7 +14438,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13979,7 +14503,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14101,7 +14629,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14280,7 +14812,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14341,7 +14877,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14402,7 +14942,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14463,7 +15007,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14524,7 +15072,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14585,7 +15137,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14642,7 +15198,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14699,7 +15259,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14760,7 +15324,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14821,7 +15389,11 @@
           <t>76.817.360-5</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14943,7 +15515,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15004,7 +15580,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15187,7 +15767,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15248,7 +15832,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15431,7 +16019,11 @@
           <t>76.872.717-1</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15492,7 +16084,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15553,7 +16149,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15675,7 +16275,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15976,7 +16580,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16037,7 +16645,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16098,7 +16710,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16220,7 +16836,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16277,7 +16897,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16460,7 +17084,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16574,7 +17202,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16635,7 +17267,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16692,7 +17328,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16753,7 +17393,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16814,7 +17458,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16875,7 +17523,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16936,7 +17588,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16997,7 +17653,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17058,7 +17718,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17119,7 +17783,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17176,7 +17844,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17298,7 +17970,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17359,7 +18035,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17481,7 +18161,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17542,7 +18226,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17603,7 +18291,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17664,7 +18356,11 @@
           <t>77.529.681-K</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17725,7 +18421,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17847,7 +18547,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17969,7 +18673,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18030,7 +18738,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18091,7 +18803,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18148,7 +18864,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18270,7 +18990,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18449,7 +19173,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18632,7 +19360,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18754,7 +19486,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18994,7 +19730,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19112,7 +19852,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19291,7 +20035,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19352,7 +20100,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19413,7 +20165,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19474,7 +20230,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19657,7 +20417,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19718,7 +20482,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19779,7 +20547,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19962,7 +20734,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20084,7 +20860,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20267,7 +21047,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20328,7 +21112,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20450,7 +21238,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20568,7 +21360,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20629,7 +21425,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20751,7 +21551,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20812,7 +21616,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20934,7 +21742,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20995,7 +21807,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21056,7 +21872,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21117,7 +21937,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21178,7 +22002,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21239,7 +22067,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21300,7 +22132,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21361,7 +22197,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21422,7 +22262,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21483,7 +22327,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21544,7 +22392,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21605,7 +22457,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21666,7 +22522,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21727,7 +22587,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21788,7 +22652,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21906,7 +22774,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22150,7 +23022,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr"/>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L358" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22272,7 +23148,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22333,7 +23213,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22390,7 +23274,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22451,7 +23339,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22634,7 +23526,11 @@
           <t>76.525.922-3</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22695,7 +23591,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22756,7 +23656,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr"/>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L368" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22817,7 +23721,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22878,7 +23786,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22939,7 +23851,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22996,7 +23912,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L372" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23179,7 +24099,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L375" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23301,7 +24225,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L377" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23362,7 +24290,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23423,7 +24355,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23484,7 +24420,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr"/>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L380" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23545,7 +24485,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L381" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23606,7 +24550,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K382" t="inlineStr"/>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L382" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23667,7 +24615,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23850,7 +24802,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L386" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24033,7 +24989,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24094,7 +25054,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr"/>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L390" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24155,7 +25119,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24216,7 +25184,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L392" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24277,7 +25249,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K393" t="inlineStr"/>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L393" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24338,7 +25314,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr"/>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L394" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24517,7 +25497,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24578,7 +25562,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L398" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24700,7 +25688,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L400" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25001,7 +25993,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K405" t="inlineStr"/>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L405" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25119,7 +26115,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K407" t="inlineStr"/>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L407" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25180,7 +26180,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25241,7 +26245,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K409" t="inlineStr"/>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L409" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25302,7 +26310,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K410" t="inlineStr"/>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L410" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25363,7 +26375,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr"/>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L411" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25485,7 +26501,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25546,7 +26566,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K414" t="inlineStr"/>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L414" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25607,7 +26631,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K415" t="inlineStr"/>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L415" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25668,7 +26696,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K416" t="inlineStr"/>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L416" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25729,7 +26761,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K417" t="inlineStr"/>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L417" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25790,7 +26826,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K418" t="inlineStr"/>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L418" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25912,7 +26952,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K420" t="inlineStr"/>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L420" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26034,7 +27078,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K422" t="inlineStr"/>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L422" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26095,7 +27143,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K423" t="inlineStr"/>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L423" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26156,7 +27208,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K424" t="inlineStr"/>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L424" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26217,7 +27273,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K425" t="inlineStr"/>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L425" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26278,7 +27338,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K426" t="inlineStr"/>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L426" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26400,7 +27464,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K428" t="inlineStr"/>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L428" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26522,7 +27590,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K430" t="inlineStr"/>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L430" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26644,7 +27716,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K432" t="inlineStr"/>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L432" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26705,7 +27781,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K433" t="inlineStr"/>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L433" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26827,7 +27907,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K435" t="inlineStr"/>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L435" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26949,7 +28033,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K437" t="inlineStr"/>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L437" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27010,7 +28098,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K438" t="inlineStr"/>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L438" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27071,7 +28163,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K439" t="inlineStr"/>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L439" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27193,7 +28289,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K441" t="inlineStr"/>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L441" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27315,7 +28415,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K443" t="inlineStr"/>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L443" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27433,7 +28537,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K445" t="inlineStr"/>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L445" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27494,7 +28602,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K446" t="inlineStr"/>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L446" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27555,7 +28667,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K447" t="inlineStr"/>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L447" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27677,7 +28793,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K449" t="inlineStr"/>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L449" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27738,7 +28858,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L450" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27917,7 +29041,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K453" t="inlineStr"/>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L453" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27978,7 +29106,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K454" t="inlineStr"/>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L454" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28039,7 +29171,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K455" t="inlineStr"/>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L455" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28100,7 +29236,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K456" t="inlineStr"/>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L456" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28222,7 +29362,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K458" t="inlineStr"/>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L458" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28405,7 +29549,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K461" t="inlineStr"/>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L461" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28466,7 +29614,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K462" t="inlineStr"/>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L462" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28649,7 +29801,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K465" t="inlineStr"/>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L465" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28710,7 +29866,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K466" t="inlineStr"/>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L466" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28893,7 +30053,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K469" t="inlineStr"/>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L469" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28954,7 +30118,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K470" t="inlineStr"/>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L470" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29076,7 +30244,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K472" t="inlineStr"/>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L472" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29198,7 +30370,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K474" t="inlineStr"/>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L474" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29320,7 +30496,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K476" t="inlineStr"/>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L476" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29381,7 +30561,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K477" t="inlineStr"/>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L477" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29686,7 +30870,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K482" t="inlineStr"/>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L482" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29869,7 +31057,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K485" t="inlineStr"/>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L485" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29926,7 +31118,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K486" t="inlineStr"/>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L486" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30044,7 +31240,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K488" t="inlineStr"/>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L488" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30166,7 +31366,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K490" t="inlineStr"/>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L490" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30227,7 +31431,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K491" t="inlineStr"/>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L491" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30288,7 +31496,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K492" t="inlineStr"/>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L492" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30410,7 +31622,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K494" t="inlineStr"/>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L494" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30593,7 +31809,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K497" t="inlineStr"/>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L497" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30715,7 +31935,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K499" t="inlineStr"/>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L499" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30776,7 +32000,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K500" t="inlineStr"/>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L500" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30837,7 +32065,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K501" t="inlineStr"/>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L501" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30898,7 +32130,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K502" t="inlineStr"/>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L502" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31020,7 +32256,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K504" t="inlineStr"/>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L504" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31081,7 +32321,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K505" t="inlineStr"/>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L505" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31142,7 +32386,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K506" t="inlineStr"/>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L506" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31203,7 +32451,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K507" t="inlineStr"/>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L507" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31264,7 +32516,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K508" t="inlineStr"/>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L508" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31325,7 +32581,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K509" t="inlineStr"/>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L509" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31386,7 +32646,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K510" t="inlineStr"/>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L510" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31447,7 +32711,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K511" t="inlineStr"/>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L511" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31569,7 +32837,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K513" t="inlineStr"/>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L513" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31691,7 +32963,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K515" t="inlineStr"/>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L515" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31752,7 +33028,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K516" t="inlineStr"/>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L516" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31813,7 +33093,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K517" t="inlineStr"/>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L517" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31935,7 +33219,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K519" t="inlineStr"/>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L519" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32053,7 +33341,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K521" t="inlineStr"/>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L521" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32171,7 +33463,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K523" t="inlineStr"/>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L523" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32293,7 +33589,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K525" t="inlineStr"/>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L525" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32411,7 +33711,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K527" t="inlineStr"/>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L527" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32472,7 +33776,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K528" t="inlineStr"/>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L528" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32533,7 +33841,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K529" t="inlineStr"/>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L529" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32594,7 +33906,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K530" t="inlineStr"/>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L530" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32716,7 +34032,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K532" t="inlineStr"/>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L532" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32777,7 +34097,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K533" t="inlineStr"/>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L533" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32899,7 +34223,11 @@
           <t>76.525.922-3</t>
         </is>
       </c>
-      <c r="K535" t="inlineStr"/>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L535" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33021,7 +34349,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K537" t="inlineStr"/>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L537" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33082,7 +34414,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K538" t="inlineStr"/>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L538" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33204,7 +34540,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K540" t="inlineStr"/>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L540" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33387,7 +34727,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K543" t="inlineStr"/>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L543" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33448,7 +34792,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K544" t="inlineStr"/>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L544" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33509,7 +34857,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K545" t="inlineStr"/>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L545" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33570,7 +34922,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K546" t="inlineStr"/>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L546" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33814,7 +35170,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K550" t="inlineStr"/>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L550" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33875,7 +35235,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K551" t="inlineStr"/>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L551" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33936,7 +35300,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K552" t="inlineStr"/>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L552" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34115,7 +35483,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K555" t="inlineStr"/>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L555" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34176,7 +35548,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K556" t="inlineStr"/>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L556" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34237,7 +35613,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K557" t="inlineStr"/>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L557" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34359,7 +35739,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K559" t="inlineStr"/>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L559" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34481,7 +35865,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K561" t="inlineStr"/>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L561" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34660,7 +36048,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K564" t="inlineStr"/>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L564" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34721,7 +36113,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K565" t="inlineStr"/>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L565" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34843,7 +36239,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K567" t="inlineStr"/>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L567" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35087,7 +36487,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K571" t="inlineStr"/>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L571" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35148,7 +36552,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K572" t="inlineStr"/>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L572" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35209,7 +36617,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K573" t="inlineStr"/>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L573" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35270,7 +36682,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K574" t="inlineStr"/>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L574" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35453,7 +36869,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K577" t="inlineStr"/>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L577" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35514,7 +36934,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K578" t="inlineStr"/>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L578" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35575,7 +36999,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K579" t="inlineStr"/>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L579" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35636,7 +37064,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K580" t="inlineStr"/>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L580" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35697,7 +37129,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K581" t="inlineStr"/>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L581" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35758,7 +37194,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K582" t="inlineStr"/>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L582" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35819,7 +37259,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K583" t="inlineStr"/>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L583" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35880,7 +37324,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K584" t="inlineStr"/>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L584" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36063,7 +37511,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K587" t="inlineStr"/>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L587" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36124,7 +37576,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K588" t="inlineStr"/>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L588" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36185,7 +37641,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K589" t="inlineStr"/>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L589" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36246,7 +37706,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K590" t="inlineStr"/>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L590" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36307,7 +37771,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K591" t="inlineStr"/>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L591" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36490,7 +37958,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K594" t="inlineStr"/>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L594" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36551,7 +38023,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K595" t="inlineStr"/>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L595" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36612,7 +38088,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K596" t="inlineStr"/>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L596" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36673,7 +38153,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K597" t="inlineStr"/>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L597" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36795,7 +38279,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K599" t="inlineStr"/>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L599" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36978,7 +38466,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K602" t="inlineStr"/>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L602" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37039,7 +38531,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K603" t="inlineStr"/>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L603" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37100,7 +38596,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K604" t="inlineStr"/>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L604" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37161,7 +38661,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K605" t="inlineStr"/>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L605" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37222,7 +38726,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K606" t="inlineStr"/>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L606" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37344,7 +38852,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K608" t="inlineStr"/>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L608" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37405,7 +38917,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K609" t="inlineStr"/>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L609" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37527,7 +39043,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K611" t="inlineStr"/>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L611" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37588,7 +39108,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K612" t="inlineStr"/>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L612" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37649,7 +39173,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K613" t="inlineStr"/>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L613" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37710,7 +39238,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K614" t="inlineStr"/>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L614" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37771,7 +39303,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K615" t="inlineStr"/>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L615" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37832,7 +39368,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K616" t="inlineStr"/>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L616" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37893,7 +39433,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K617" t="inlineStr"/>
+      <c r="K617" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L617" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37954,7 +39498,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K618" t="inlineStr"/>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L618" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38011,7 +39559,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K619" t="inlineStr"/>
+      <c r="K619" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L619" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38133,7 +39685,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K621" t="inlineStr"/>
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L621" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38316,7 +39872,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K624" t="inlineStr"/>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L624" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38377,7 +39937,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K625" t="inlineStr"/>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L625" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38438,7 +40002,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K626" t="inlineStr"/>
+      <c r="K626" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L626" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38560,7 +40128,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K628" t="inlineStr"/>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L628" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38621,7 +40193,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K629" t="inlineStr"/>
+      <c r="K629" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L629" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38682,7 +40258,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K630" t="inlineStr"/>
+      <c r="K630" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L630" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38743,7 +40323,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K631" t="inlineStr"/>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L631" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38865,7 +40449,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K633" t="inlineStr"/>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L633" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38926,7 +40514,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K634" t="inlineStr"/>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L634" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38987,7 +40579,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K635" t="inlineStr"/>
+      <c r="K635" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L635" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39166,7 +40762,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K638" t="inlineStr"/>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L638" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39227,7 +40827,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K639" t="inlineStr"/>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L639" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39288,7 +40892,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K640" t="inlineStr"/>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L640" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39349,7 +40957,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K641" t="inlineStr"/>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L641" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39471,7 +41083,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K643" t="inlineStr"/>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L643" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39532,7 +41148,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K644" t="inlineStr"/>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L644" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39650,7 +41270,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K646" t="inlineStr"/>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L646" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39711,7 +41335,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K647" t="inlineStr"/>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L647" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39772,7 +41400,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K648" t="inlineStr"/>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L648" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40012,7 +41644,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K652" t="inlineStr"/>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L652" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40073,7 +41709,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K653" t="inlineStr"/>
+      <c r="K653" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L653" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40134,7 +41774,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K654" t="inlineStr"/>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L654" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40256,7 +41900,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K656" t="inlineStr"/>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L656" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40317,7 +41965,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K657" t="inlineStr"/>
+      <c r="K657" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L657" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40435,7 +42087,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K659" t="inlineStr"/>
+      <c r="K659" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L659" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40496,7 +42152,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K660" t="inlineStr"/>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L660" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40557,7 +42217,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K661" t="inlineStr"/>
+      <c r="K661" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L661" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40618,7 +42282,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K662" t="inlineStr"/>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L662" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40740,7 +42408,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K664" t="inlineStr"/>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L664" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40801,7 +42473,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K665" t="inlineStr"/>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L665" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40923,7 +42599,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K667" t="inlineStr"/>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L667" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41106,7 +42786,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K670" t="inlineStr"/>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L670" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41167,7 +42851,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K671" t="inlineStr"/>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L671" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41228,7 +42916,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K672" t="inlineStr"/>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L672" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41346,7 +43038,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K674" t="inlineStr"/>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L674" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41468,7 +43164,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K676" t="inlineStr"/>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L676" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41529,7 +43229,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K677" t="inlineStr"/>
+      <c r="K677" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L677" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41590,7 +43294,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K678" t="inlineStr"/>
+      <c r="K678" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L678" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41651,7 +43359,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K679" t="inlineStr"/>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L679" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41773,7 +43485,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K681" t="inlineStr"/>
+      <c r="K681" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L681" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41834,7 +43550,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K682" t="inlineStr"/>
+      <c r="K682" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L682" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41895,7 +43615,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K683" t="inlineStr"/>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L683" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41956,7 +43680,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K684" t="inlineStr"/>
+      <c r="K684" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L684" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42017,7 +43745,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K685" t="inlineStr"/>
+      <c r="K685" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L685" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42078,7 +43810,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K686" t="inlineStr"/>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L686" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42135,7 +43871,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K687" t="inlineStr"/>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L687" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42196,7 +43936,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K688" t="inlineStr"/>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L688" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42318,7 +44062,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K690" t="inlineStr"/>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L690" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42375,7 +44123,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K691" t="inlineStr"/>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L691" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42497,7 +44249,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K693" t="inlineStr"/>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L693" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42558,7 +44314,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K694" t="inlineStr"/>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L694" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42680,7 +44440,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K696" t="inlineStr"/>
+      <c r="K696" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L696" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42802,7 +44566,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K698" t="inlineStr"/>
+      <c r="K698" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L698" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42863,7 +44631,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K699" t="inlineStr"/>
+      <c r="K699" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L699" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43103,7 +44875,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K703" t="inlineStr"/>
+      <c r="K703" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L703" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43286,7 +45062,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K706" t="inlineStr"/>
+      <c r="K706" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L706" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43347,7 +45127,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K707" t="inlineStr"/>
+      <c r="K707" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L707" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43408,7 +45192,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K708" t="inlineStr"/>
+      <c r="K708" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L708" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43469,7 +45257,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K709" t="inlineStr"/>
+      <c r="K709" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L709" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43530,7 +45322,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K710" t="inlineStr"/>
+      <c r="K710" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L710" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43591,7 +45387,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K711" t="inlineStr"/>
+      <c r="K711" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L711" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43713,7 +45513,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K713" t="inlineStr"/>
+      <c r="K713" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L713" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43892,7 +45696,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K716" t="inlineStr"/>
+      <c r="K716" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L716" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43953,7 +45761,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K717" t="inlineStr"/>
+      <c r="K717" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L717" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44075,7 +45887,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K719" t="inlineStr"/>
+      <c r="K719" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L719" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44197,7 +46013,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K721" t="inlineStr"/>
+      <c r="K721" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L721" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44258,7 +46078,11 @@
           <t>77.623.039-1</t>
         </is>
       </c>
-      <c r="K722" t="inlineStr"/>
+      <c r="K722" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L722" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44315,7 +46139,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K723" t="inlineStr"/>
+      <c r="K723" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L723" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44376,7 +46204,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K724" t="inlineStr"/>
+      <c r="K724" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L724" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44559,7 +46391,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K727" t="inlineStr"/>
+      <c r="K727" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L727" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44620,7 +46456,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K728" t="inlineStr"/>
+      <c r="K728" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L728" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44681,7 +46521,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K729" t="inlineStr"/>
+      <c r="K729" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L729" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44738,7 +46582,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K730" t="inlineStr"/>
+      <c r="K730" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L730" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44921,7 +46769,11 @@
           <t>77.623.039-1</t>
         </is>
       </c>
-      <c r="K733" t="inlineStr"/>
+      <c r="K733" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L733" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45039,7 +46891,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K735" t="inlineStr"/>
+      <c r="K735" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L735" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45283,7 +47139,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K739" t="inlineStr"/>
+      <c r="K739" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L739" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45466,7 +47326,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K742" t="inlineStr"/>
+      <c r="K742" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L742" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45527,7 +47391,11 @@
           <t>76.525.922-3</t>
         </is>
       </c>
-      <c r="K743" t="inlineStr"/>
+      <c r="K743" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L743" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45588,7 +47456,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K744" t="inlineStr"/>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L744" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45767,7 +47639,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K747" t="inlineStr"/>
+      <c r="K747" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L747" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45889,7 +47765,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K749" t="inlineStr"/>
+      <c r="K749" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L749" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46072,7 +47952,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K752" t="inlineStr"/>
+      <c r="K752" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L752" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46133,7 +48017,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K753" t="inlineStr"/>
+      <c r="K753" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L753" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46194,7 +48082,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K754" t="inlineStr"/>
+      <c r="K754" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L754" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46377,7 +48269,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K757" t="inlineStr"/>
+      <c r="K757" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L757" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46438,7 +48334,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K758" t="inlineStr"/>
+      <c r="K758" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L758" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46495,7 +48395,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K759" t="inlineStr"/>
+      <c r="K759" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L759" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46556,7 +48460,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K760" t="inlineStr"/>
+      <c r="K760" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L760" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46617,7 +48525,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K761" t="inlineStr"/>
+      <c r="K761" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L761" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46739,7 +48651,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K763" t="inlineStr"/>
+      <c r="K763" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L763" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46922,7 +48838,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K766" t="inlineStr"/>
+      <c r="K766" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L766" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46983,7 +48903,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K767" t="inlineStr"/>
+      <c r="K767" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L767" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47105,7 +49029,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K769" t="inlineStr"/>
+      <c r="K769" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L769" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47349,7 +49277,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K773" t="inlineStr"/>
+      <c r="K773" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L773" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47471,7 +49403,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K775" t="inlineStr"/>
+      <c r="K775" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L775" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47532,7 +49468,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K776" t="inlineStr"/>
+      <c r="K776" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L776" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47715,7 +49655,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K779" t="inlineStr"/>
+      <c r="K779" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L779" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47776,7 +49720,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K780" t="inlineStr"/>
+      <c r="K780" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L780" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47837,7 +49785,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K781" t="inlineStr"/>
+      <c r="K781" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L781" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47898,7 +49850,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K782" t="inlineStr"/>
+      <c r="K782" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L782" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47959,7 +49915,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K783" t="inlineStr"/>
+      <c r="K783" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L783" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48081,7 +50041,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K785" t="inlineStr"/>
+      <c r="K785" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L785" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48138,7 +50102,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K786" t="inlineStr"/>
+      <c r="K786" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L786" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48199,7 +50167,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K787" t="inlineStr"/>
+      <c r="K787" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L787" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48256,7 +50228,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K788" t="inlineStr"/>
+      <c r="K788" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L788" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48317,7 +50293,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K789" t="inlineStr"/>
+      <c r="K789" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L789" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48378,7 +50358,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K790" t="inlineStr"/>
+      <c r="K790" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L790" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48439,7 +50423,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K791" t="inlineStr"/>
+      <c r="K791" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L791" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48561,7 +50549,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K793" t="inlineStr"/>
+      <c r="K793" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L793" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48622,7 +50614,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K794" t="inlineStr"/>
+      <c r="K794" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L794" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48683,7 +50679,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K795" t="inlineStr"/>
+      <c r="K795" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L795" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48744,7 +50744,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K796" t="inlineStr"/>
+      <c r="K796" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L796" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48866,7 +50870,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K798" t="inlineStr"/>
+      <c r="K798" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L798" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48927,7 +50935,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K799" t="inlineStr"/>
+      <c r="K799" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L799" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49049,7 +51061,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K801" t="inlineStr"/>
+      <c r="K801" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L801" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49171,7 +51187,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K803" t="inlineStr"/>
+      <c r="K803" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L803" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49293,7 +51313,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K805" t="inlineStr"/>
+      <c r="K805" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L805" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49415,7 +51439,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K807" t="inlineStr"/>
+      <c r="K807" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L807" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49476,7 +51504,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K808" t="inlineStr"/>
+      <c r="K808" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L808" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49537,7 +51569,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K809" t="inlineStr"/>
+      <c r="K809" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L809" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49659,7 +51695,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K811" t="inlineStr"/>
+      <c r="K811" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L811" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49720,7 +51760,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K812" t="inlineStr"/>
+      <c r="K812" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L812" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49903,7 +51947,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K815" t="inlineStr"/>
+      <c r="K815" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L815" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49960,7 +52008,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K816" t="inlineStr"/>
+      <c r="K816" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L816" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50082,7 +52134,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K818" t="inlineStr"/>
+      <c r="K818" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L818" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50143,7 +52199,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K819" t="inlineStr"/>
+      <c r="K819" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L819" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50265,7 +52325,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K821" t="inlineStr"/>
+      <c r="K821" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L821" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50322,7 +52386,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K822" t="inlineStr"/>
+      <c r="K822" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L822" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50383,7 +52451,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K823" t="inlineStr"/>
+      <c r="K823" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L823" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50444,7 +52516,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K824" t="inlineStr"/>
+      <c r="K824" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L824" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50688,7 +52764,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K828" t="inlineStr"/>
+      <c r="K828" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L828" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50867,7 +52947,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K831" t="inlineStr"/>
+      <c r="K831" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L831" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50928,7 +53012,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K832" t="inlineStr"/>
+      <c r="K832" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L832" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50989,7 +53077,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K833" t="inlineStr"/>
+      <c r="K833" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L833" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51050,7 +53142,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K834" t="inlineStr"/>
+      <c r="K834" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L834" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51111,7 +53207,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K835" t="inlineStr"/>
+      <c r="K835" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L835" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51172,7 +53272,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K836" t="inlineStr"/>
+      <c r="K836" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L836" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51294,7 +53398,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K838" t="inlineStr"/>
+      <c r="K838" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L838" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51355,7 +53463,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K839" t="inlineStr"/>
+      <c r="K839" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L839" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51416,7 +53528,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K840" t="inlineStr"/>
+      <c r="K840" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L840" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51477,7 +53593,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K841" t="inlineStr"/>
+      <c r="K841" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L841" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51599,7 +53719,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K843" t="inlineStr"/>
+      <c r="K843" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L843" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51843,7 +53967,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K847" t="inlineStr"/>
+      <c r="K847" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L847" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/ene-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/ene-2025.xlsx
@@ -2200,7 +2200,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3952,7 +3956,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4777,7 +4785,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5350,7 +5362,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5854,7 +5870,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5980,7 +6000,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11268,7 +11292,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11455,7 +11483,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11951,7 +11983,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12264,7 +12300,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12520,7 +12560,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13276,7 +13320,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14694,7 +14742,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15897,7 +15949,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15958,7 +16014,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16401,7 +16461,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17909,7 +17973,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18100,7 +18168,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18612,7 +18684,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19299,7 +19375,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19425,7 +19505,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19791,7 +19875,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19974,7 +20062,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20295,7 +20387,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20356,7 +20452,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20925,7 +21025,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21303,7 +21407,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21490,7 +21598,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24680,7 +24792,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K384" t="inlineStr"/>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L384" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24741,7 +24857,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr"/>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L385" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24867,7 +24987,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25436,7 +25560,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K396" t="inlineStr"/>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L396" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25627,7 +25755,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr"/>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L399" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25753,7 +25885,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25932,7 +26068,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K404" t="inlineStr"/>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L404" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26054,7 +26194,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L406" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27655,7 +27799,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L431" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29427,7 +29575,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K459" t="inlineStr"/>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L459" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29488,7 +29640,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K460" t="inlineStr"/>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L460" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30183,7 +30339,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K471" t="inlineStr"/>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L471" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30935,7 +31095,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K483" t="inlineStr"/>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L483" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30996,7 +31160,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K484" t="inlineStr"/>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L484" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31183,7 +31351,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K487" t="inlineStr"/>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L487" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31561,7 +31733,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K493" t="inlineStr"/>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L493" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32776,7 +32952,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K512" t="inlineStr"/>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L512" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33158,7 +33338,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K518" t="inlineStr"/>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L518" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34479,7 +34663,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K539" t="inlineStr"/>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L539" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34666,7 +34854,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K542" t="inlineStr"/>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L542" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35109,7 +35301,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K549" t="inlineStr"/>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L549" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35365,7 +35561,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K553" t="inlineStr"/>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L553" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36304,7 +36504,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K568" t="inlineStr"/>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L568" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36426,7 +36630,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K570" t="inlineStr"/>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L570" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36747,7 +36955,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K575" t="inlineStr"/>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L575" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38344,7 +38556,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K600" t="inlineStr"/>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L600" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39811,7 +40027,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K623" t="inlineStr"/>
+      <c r="K623" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L623" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40701,7 +40921,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K637" t="inlineStr"/>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L637" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41213,7 +41437,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K645" t="inlineStr"/>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L645" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41839,7 +42067,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K655" t="inlineStr"/>
+      <c r="K655" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L655" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42030,7 +42262,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K658" t="inlineStr"/>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L658" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42347,7 +42583,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K663" t="inlineStr"/>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L663" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42664,7 +42904,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K668" t="inlineStr"/>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L668" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42725,7 +42969,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K669" t="inlineStr"/>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L669" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44188,7 +44436,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K692" t="inlineStr"/>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L692" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44379,7 +44631,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K695" t="inlineStr"/>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L695" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44696,7 +44952,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K700" t="inlineStr"/>
+      <c r="K700" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L700" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44940,7 +45200,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K704" t="inlineStr"/>
+      <c r="K704" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L704" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45001,7 +45265,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K705" t="inlineStr"/>
+      <c r="K705" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L705" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46269,7 +46537,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K725" t="inlineStr"/>
+      <c r="K725" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L725" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46330,7 +46602,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K726" t="inlineStr"/>
+      <c r="K726" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L726" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46834,7 +47110,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K734" t="inlineStr"/>
+      <c r="K734" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L734" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46956,7 +47236,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K736" t="inlineStr"/>
+      <c r="K736" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L736" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47017,7 +47301,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K737" t="inlineStr"/>
+      <c r="K737" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L737" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47265,7 +47553,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K741" t="inlineStr"/>
+      <c r="K741" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L741" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48716,7 +49008,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K764" t="inlineStr"/>
+      <c r="K764" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L764" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49155,7 +49451,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K771" t="inlineStr"/>
+      <c r="K771" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L771" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50809,7 +51109,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K797" t="inlineStr"/>
+      <c r="K797" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L797" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51886,7 +52190,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K814" t="inlineStr"/>
+      <c r="K814" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L814" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53845,7 +54153,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K845" t="inlineStr"/>
+      <c r="K845" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L845" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/ene-2025.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/ene-2025.xlsx
@@ -677,7 +677,11 @@
           <t>SERVICIO DE SALUD SUR HOSPITAL EXEQUIEL</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>DIMERC S A</t>
@@ -735,7 +739,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1689,7 +1693,11 @@
           <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>MARYUN Seguridad Industrial</t>
@@ -2006,7 +2014,11 @@
           <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>GRUPO DK SERVICIOS LIMITADA</t>
@@ -2189,7 +2201,11 @@
           <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>COMERCIAL AGUSTIN LIMITADA</t>
@@ -2685,7 +2701,11 @@
           <t>SERVICIO SALUD OCCIDENTE HOSPITAL DR FELIX BULNES CERDA</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr">
         <is>
           <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
@@ -2803,7 +2823,11 @@
           <t>I MUNICIPALIDAD DE LIMACHE</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr">
         <is>
           <t>DISTRIBUIDORA MANZANO S A</t>
@@ -3307,7 +3331,11 @@
           <t>Corporación Municipal de Deportes de Ñuñoa</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr">
         <is>
           <t>WINKLER LIMITADA</t>
@@ -4323,7 +4351,11 @@
           <t>SERVICIO SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr">
         <is>
           <t>DIMERC S A</t>
@@ -6858,7 +6890,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -7127,7 +7159,11 @@
           <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr"/>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I106" t="inlineStr">
         <is>
           <t>SCANNO SPA</t>
@@ -8448,7 +8484,11 @@
           <t>I MUNICIPALIDAD DE TOME</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr"/>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="I127" t="inlineStr">
         <is>
           <t>COMERCIAL MUNOZ Y COMPANIA LIMITADA</t>
@@ -8765,7 +8805,11 @@
           <t>SERVICIO NACIONAL ARAUCANIA SUR HOSPITAL DR ABRAHAM GODOY PENA LAUTARO</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr"/>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="I132" t="inlineStr">
         <is>
           <t>COMERCIALIZADORA PRANDELLI LIMITADA</t>
@@ -9392,7 +9436,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9457,7 +9501,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9586,7 +9630,11 @@
           <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr"/>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="I145" t="inlineStr">
         <is>
           <t>DIMERC S A</t>
@@ -9821,7 +9869,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -9834,7 +9882,11 @@
           <t>UNIVERSIDAD METROPOLITANA DE CIENCIAS DE LA EDUCACION</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr"/>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I149" t="inlineStr">
         <is>
           <t>Marco Antonio</t>
@@ -9878,7 +9930,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -11216,7 +11268,11 @@
           <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr"/>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="I171" t="inlineStr">
         <is>
           <t>PROVEEDORES INTEGRALES PRISA S A</t>
@@ -11339,7 +11395,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11655,7 +11711,11 @@
           <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr"/>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="I178" t="inlineStr">
         <is>
           <t>WINKLER LIMITADA</t>
@@ -11846,7 +11906,11 @@
           <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr"/>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="I181" t="inlineStr">
         <is>
           <t>DISTRIBUIDORA MANZANO S A</t>
@@ -14853,7 +14917,11 @@
           <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr"/>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="I228" t="inlineStr">
         <is>
           <t>DIMERC S A</t>
@@ -15239,7 +15307,11 @@
           <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
-      <c r="H234" t="inlineStr"/>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I234" t="inlineStr">
         <is>
           <t>DIMERC S A</t>
@@ -15300,7 +15372,11 @@
           <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
-      <c r="H235" t="inlineStr"/>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I235" t="inlineStr">
         <is>
           <t>DIMERC S A</t>
@@ -16126,7 +16202,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -16633,7 +16709,11 @@
           <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE LAJA</t>
         </is>
       </c>
-      <c r="H256" t="inlineStr"/>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="I256" t="inlineStr">
         <is>
           <t>DIMERC S A</t>
@@ -16950,7 +17030,11 @@
           <t>SERVICIO DE SALUD OCCIDENTE HOSPITAL SAN JUAN DE DIOS</t>
         </is>
       </c>
-      <c r="H261" t="inlineStr"/>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I261" t="inlineStr">
         <is>
           <t>PROVEEDORES INTEGRALES PRISA S A</t>
@@ -17198,7 +17282,11 @@
           <t>HOSPITAL BASE OSORNO</t>
         </is>
       </c>
-      <c r="H265" t="inlineStr"/>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="I265" t="inlineStr">
         <is>
           <t>MARYUN Seguridad Industrial</t>
@@ -17255,7 +17343,11 @@
           <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
-      <c r="H266" t="inlineStr"/>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I266" t="inlineStr">
         <is>
           <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
@@ -17381,7 +17473,11 @@
           <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
-      <c r="H268" t="inlineStr"/>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="I268" t="inlineStr">
         <is>
           <t>DIMERC S A</t>
@@ -17897,7 +17993,11 @@
           <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
-      <c r="H276" t="inlineStr"/>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="I276" t="inlineStr">
         <is>
           <t>PROVEEDORES INTEGRALES PRISA S A</t>
@@ -18929,7 +19029,11 @@
           <t>HOSPITAL DE QUILPUE</t>
         </is>
       </c>
-      <c r="H292" t="inlineStr"/>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="I292" t="inlineStr">
         <is>
           <t>DIMERC S A</t>
@@ -19113,10 +19217,14 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
-        </is>
-      </c>
-      <c r="H295" t="inlineStr"/>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="I295" t="inlineStr">
         <is>
           <t>SCANNO SPA</t>
@@ -19617,7 +19725,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -19681,7 +19789,11 @@
           <t>SERVICIO DE SALUD OCCIDENTE INSTITUTO TRAUMATOLOGICO DE SANTIAGO</t>
         </is>
       </c>
-      <c r="H304" t="inlineStr"/>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I304" t="inlineStr">
         <is>
           <t>COMERCIALIZADORA VYB</t>
@@ -19864,7 +19976,11 @@
           <t>SERVICIO DE SALUD BIO BIO HOSPITAL SANTA BARBARA</t>
         </is>
       </c>
-      <c r="H307" t="inlineStr"/>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="I307" t="inlineStr">
         <is>
           <t>COMERCIAL AGUSTIN LIMITADA</t>
@@ -19990,7 +20106,11 @@
           <t>SERVICIO NACIONAL ARAUCANIA SUR HOSPITAL DR ABRAHAM GODOY PENA LAUTARO</t>
         </is>
       </c>
-      <c r="H309" t="inlineStr"/>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="I309" t="inlineStr">
         <is>
           <t>prodesa</t>
@@ -21457,7 +21577,11 @@
           <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
-      <c r="H332" t="inlineStr"/>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="I332" t="inlineStr">
         <is>
           <t>DIMERC S A</t>
@@ -22814,7 +22938,11 @@
           <t>I MUNICIPALIDAD DE SAN FELIPE</t>
         </is>
       </c>
-      <c r="H353" t="inlineStr"/>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="I353" t="inlineStr">
         <is>
           <t>MULTI SAFE SPA</t>
@@ -23375,7 +23503,11 @@
           <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE T</t>
         </is>
       </c>
-      <c r="H362" t="inlineStr"/>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I362" t="inlineStr">
         <is>
           <t>DIMERC S A</t>
@@ -24013,7 +24145,11 @@
           <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
-      <c r="H372" t="inlineStr"/>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I372" t="inlineStr">
         <is>
           <t>DIMERC S A</t>
@@ -25488,7 +25624,11 @@
           <t>SERVICIO DE SALUD VALDIVIA HOSPITAL BASE</t>
         </is>
       </c>
-      <c r="H395" t="inlineStr"/>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
       <c r="I395" t="inlineStr">
         <is>
           <t>SOC COMERCIAL CINTEC LIMITADA</t>
@@ -26057,7 +26197,11 @@
           <t>I MUNICIPALIDAD DE CONSTITUCION</t>
         </is>
       </c>
-      <c r="H404" t="inlineStr"/>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="I404" t="inlineStr">
         <is>
           <t>COMERCIAL AGUSTIN LIMITADA</t>
@@ -26183,7 +26327,11 @@
           <t>I MUNICIPALIDAD DE PADRE HURTADO</t>
         </is>
       </c>
-      <c r="H406" t="inlineStr"/>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I406" t="inlineStr">
         <is>
           <t>COMERCIAL AGUSTIN LIMITADA</t>
@@ -28545,7 +28693,7 @@
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H443" t="inlineStr">
@@ -28674,7 +28822,11 @@
           <t>I MUNICIPALIDAD DE LIMACHE</t>
         </is>
       </c>
-      <c r="H445" t="inlineStr"/>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="I445" t="inlineStr">
         <is>
           <t>MG PUBLICIDAD Y EVENTOS SPA</t>
@@ -29114,10 +29266,14 @@
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
-        </is>
-      </c>
-      <c r="H452" t="inlineStr"/>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I452" t="inlineStr">
         <is>
           <t>COMERCIALIZADORA VYB</t>
@@ -31275,7 +31431,11 @@
           <t>SERVICIO SALUD OCCIDENTE HOSPITAL DR FELIX BULNES CERDA</t>
         </is>
       </c>
-      <c r="H486" t="inlineStr"/>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I486" t="inlineStr">
         <is>
           <t>COMERCIAL RED OFFICE LIMITADA</t>
@@ -31401,7 +31561,11 @@
           <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
-      <c r="H488" t="inlineStr"/>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="I488" t="inlineStr">
         <is>
           <t>DIMERC S A</t>
@@ -31585,7 +31749,7 @@
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H491" t="inlineStr">
@@ -32739,7 +32903,7 @@
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H509" t="inlineStr">
@@ -33514,7 +33678,11 @@
           <t>HOSPITAL METROPOLITANO DE SANTIAGO</t>
         </is>
       </c>
-      <c r="H521" t="inlineStr"/>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I521" t="inlineStr">
         <is>
           <t>MG PUBLICIDAD Y EVENTOS SPA</t>
@@ -33575,7 +33743,11 @@
           <t>CENTRO DE REFERENCIA DE SALUD DE MAIPU</t>
         </is>
       </c>
-      <c r="H522" t="inlineStr"/>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I522" t="inlineStr">
         <is>
           <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
@@ -33884,7 +34056,11 @@
           <t>HOSPITAL METROPOLITANO DE SANTIAGO</t>
         </is>
       </c>
-      <c r="H527" t="inlineStr"/>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I527" t="inlineStr">
         <is>
           <t>MG PUBLICIDAD Y EVENTOS SPA</t>
@@ -35611,7 +35787,11 @@
           <t>HOSPITAL DE QUILPUE</t>
         </is>
       </c>
-      <c r="H554" t="inlineStr"/>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="I554" t="inlineStr">
         <is>
           <t>DISTRIBUIDORA MANZANO S A</t>
@@ -35785,7 +35965,7 @@
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F557" t="inlineStr">
@@ -36237,7 +36417,11 @@
           <t>I MUNICIPALIDAD DE LA COMUNA DE EL BOSQUE</t>
         </is>
       </c>
-      <c r="H564" t="inlineStr"/>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I564" t="inlineStr">
         <is>
           <t>DIMERC S A</t>
@@ -39764,7 +39948,11 @@
           <t>I MUNICIPALIDAD DE SAN FERNANDO</t>
         </is>
       </c>
-      <c r="H619" t="inlineStr"/>
+      <c r="H619" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="I619" t="inlineStr">
         <is>
           <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
@@ -40204,7 +40392,7 @@
       </c>
       <c r="G626" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H626" t="inlineStr">
@@ -40849,7 +41037,11 @@
           <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
-      <c r="H636" t="inlineStr"/>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I636" t="inlineStr">
         <is>
           <t>SCANNO SPA</t>
@@ -41088,7 +41280,7 @@
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F640" t="inlineStr">
@@ -41487,7 +41679,11 @@
           <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
-      <c r="H646" t="inlineStr"/>
+      <c r="H646" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I646" t="inlineStr">
         <is>
           <t>DIMERC S A</t>
@@ -41800,7 +41996,11 @@
           <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
-      <c r="H651" t="inlineStr"/>
+      <c r="H651" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I651" t="inlineStr">
         <is>
           <t>Barron Vieyra International Ltda.</t>
@@ -42244,7 +42444,7 @@
       </c>
       <c r="G658" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H658" t="inlineStr">
@@ -42312,7 +42512,11 @@
           <t>SERVICIO DE SALUD NUBLE HOSPITAL DE QUIRIHUE</t>
         </is>
       </c>
-      <c r="H659" t="inlineStr"/>
+      <c r="H659" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="I659" t="inlineStr">
         <is>
           <t>SOLUCIONES INTEGRALES DE LIMPIEZA LIMITADA</t>
@@ -43214,7 +43418,11 @@
           <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
-      <c r="H673" t="inlineStr"/>
+      <c r="H673" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="I673" t="inlineStr">
         <is>
           <t>DISTRIBUIDORA MANZANO S A</t>
@@ -43845,7 +44053,7 @@
       </c>
       <c r="G683" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H683" t="inlineStr">
@@ -44108,7 +44316,11 @@
           <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
-      <c r="H687" t="inlineStr"/>
+      <c r="H687" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I687" t="inlineStr">
         <is>
           <t>MG PUBLICIDAD Y EVENTOS SPA</t>
@@ -44360,7 +44572,11 @@
           <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
-      <c r="H691" t="inlineStr"/>
+      <c r="H691" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="I691" t="inlineStr">
         <is>
           <t>PROVEEDORES INTEGRALES PRISA S A</t>
@@ -45124,7 +45340,11 @@
           <t>I MUNICIPALIDAD DE FUTRONO</t>
         </is>
       </c>
-      <c r="H703" t="inlineStr"/>
+      <c r="H703" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
       <c r="I703" t="inlineStr">
         <is>
           <t>PROVEEDORES INTEGRALES PRISA S A</t>
@@ -45889,7 +46109,7 @@
       </c>
       <c r="G715" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H715" t="inlineStr">
@@ -45950,10 +46170,14 @@
       </c>
       <c r="G716" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
-        </is>
-      </c>
-      <c r="H716" t="inlineStr"/>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H716" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I716" t="inlineStr">
         <is>
           <t>PROVEEDORES INTEGRALES PRISA S A</t>
@@ -46396,7 +46620,11 @@
           <t>SERVICIO DE SALUD ORIENTE HOSPITAL DEL SALVADOR</t>
         </is>
       </c>
-      <c r="H723" t="inlineStr"/>
+      <c r="H723" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I723" t="inlineStr">
         <is>
           <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
@@ -46847,7 +47075,11 @@
           <t>HOSPITAL COMPLEJO ASISTENCIAL PADRE LAS CASAS</t>
         </is>
       </c>
-      <c r="H730" t="inlineStr"/>
+      <c r="H730" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="I730" t="inlineStr">
         <is>
           <t>PROVEEDORES INTEGRALES PRISA S A</t>
@@ -47160,7 +47392,11 @@
           <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
-      <c r="H735" t="inlineStr"/>
+      <c r="H735" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="I735" t="inlineStr">
         <is>
           <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
@@ -47798,7 +48034,11 @@
           <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
-      <c r="H745" t="inlineStr"/>
+      <c r="H745" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="I745" t="inlineStr">
         <is>
           <t>PROVEEDORES INTEGRALES DEL SUR S.A.</t>
@@ -48676,7 +48916,11 @@
           <t>I MUNICIPALIDAD DE ILLAPEL</t>
         </is>
       </c>
-      <c r="H759" t="inlineStr"/>
+      <c r="H759" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="I759" t="inlineStr">
         <is>
           <t>DIMERC S A</t>
@@ -48925,7 +49169,7 @@
       </c>
       <c r="G763" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H763" t="inlineStr">
@@ -50391,7 +50635,11 @@
           <t>INSTITUTO NACIONAL DEL TORAX</t>
         </is>
       </c>
-      <c r="H786" t="inlineStr"/>
+      <c r="H786" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I786" t="inlineStr">
         <is>
           <t>PROVEEDORES INTEGRALES PRISA S A</t>
@@ -50517,7 +50765,11 @@
           <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
-      <c r="H788" t="inlineStr"/>
+      <c r="H788" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I788" t="inlineStr">
         <is>
           <t>PROVEEDORES INTEGRALES PRISA S A</t>
@@ -50961,7 +51213,7 @@
       </c>
       <c r="G795" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H795" t="inlineStr">
@@ -51402,7 +51654,7 @@
       </c>
       <c r="E802" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F802" t="inlineStr">
@@ -52305,7 +52557,11 @@
           <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
-      <c r="H816" t="inlineStr"/>
+      <c r="H816" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="I816" t="inlineStr">
         <is>
           <t>PROVEEDORES INTEGRALES PRISA S A</t>
@@ -52683,7 +52939,11 @@
           <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
-      <c r="H822" t="inlineStr"/>
+      <c r="H822" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="I822" t="inlineStr">
         <is>
           <t>DIMERC S A</t>
@@ -53183,7 +53443,11 @@
           <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
-      <c r="H830" t="inlineStr"/>
+      <c r="H830" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="I830" t="inlineStr">
         <is>
           <t>SOC COMERCIAL CINTEC LIMITADA</t>
